--- a/AS.xlsx
+++ b/AS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358139E9-BA89-45F3-B921-5508A295B596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D75A897-FEE2-4E1B-981C-3B97BE1CC67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{53BA411E-2A41-4FEC-A342-AE8C41391E29}"/>
   </bookViews>
@@ -324,7 +324,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -345,6 +345,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -701,7 +702,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>34.25</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -709,10 +710,10 @@
         <v>3</v>
       </c>
       <c r="J3" s="6">
-        <v>556.19940199999996</v>
+        <v>556.80298600000003</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -724,7 +725,7 @@
       </c>
       <c r="J4" s="7">
         <f>+J2*J3</f>
-        <v>19049.829518499999</v>
+        <v>22544.952903140002</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -735,10 +736,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="7">
-        <v>353.3</v>
+        <v>652.29999999999995</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -746,11 +747,11 @@
         <v>6</v>
       </c>
       <c r="J6" s="7">
-        <f>791.9+259.5</f>
-        <v>1051.4000000000001</v>
+        <f>792.3+142.8</f>
+        <v>935.09999999999991</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -759,7 +760,7 @@
       </c>
       <c r="J7" s="7">
         <f>+J4-J5+J6</f>
-        <v>19747.929518500001</v>
+        <v>22827.752903140001</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -891,6 +892,9 @@
         <f>+J3</f>
         <v>223</v>
       </c>
+      <c r="S3" s="2">
+        <v>288</v>
+      </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
@@ -938,6 +942,9 @@
         <f t="shared" ref="R4:R5" si="1">+J4</f>
         <v>229</v>
       </c>
+      <c r="S4" s="2">
+        <v>331</v>
+      </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
@@ -985,6 +992,9 @@
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
+      <c r="S5" s="2">
+        <v>84</v>
+      </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
@@ -1049,7 +1059,7 @@
       </c>
       <c r="S6" s="4">
         <f>+SUM(S3:S5)</f>
-        <v>0</v>
+        <v>703</v>
       </c>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.2">
@@ -1103,7 +1113,9 @@
       <c r="M8" s="6">
         <v>528.5</v>
       </c>
-      <c r="N8" s="6"/>
+      <c r="N8" s="6">
+        <v>596.20000000000005</v>
+      </c>
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="6">
@@ -1112,7 +1124,9 @@
       <c r="R8" s="6">
         <v>1606</v>
       </c>
-      <c r="S8" s="6"/>
+      <c r="S8" s="6">
+        <v>1805.8</v>
+      </c>
       <c r="T8" s="6"/>
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
@@ -1174,7 +1188,9 @@
       <c r="M9" s="6">
         <v>574.20000000000005</v>
       </c>
-      <c r="N9" s="6"/>
+      <c r="N9" s="6">
+        <v>691.3</v>
+      </c>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
       <c r="Q9" s="6">
@@ -1183,7 +1199,9 @@
       <c r="R9" s="6">
         <v>1762.1000000000001</v>
       </c>
-      <c r="S9" s="6"/>
+      <c r="S9" s="6">
+        <v>2125.6</v>
+      </c>
       <c r="T9" s="6"/>
       <c r="U9" s="6"/>
       <c r="V9" s="6"/>
@@ -1245,7 +1263,9 @@
       <c r="M10" s="6">
         <v>461.5</v>
       </c>
-      <c r="N10" s="6"/>
+      <c r="N10" s="6">
+        <v>544.20000000000005</v>
+      </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
       <c r="Q10" s="6">
@@ -1254,7 +1274,9 @@
       <c r="R10" s="6">
         <v>1297.5</v>
       </c>
-      <c r="S10" s="6"/>
+      <c r="S10" s="6">
+        <v>1861.9</v>
+      </c>
       <c r="T10" s="6"/>
       <c r="U10" s="6"/>
       <c r="V10" s="6"/>
@@ -1316,7 +1338,9 @@
       <c r="M11" s="6">
         <v>192.1</v>
       </c>
-      <c r="N11" s="6"/>
+      <c r="N11" s="6">
+        <v>269.39999999999998</v>
+      </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
       <c r="Q11" s="6">
@@ -1325,7 +1349,9 @@
       <c r="R11" s="6">
         <v>512.4</v>
       </c>
-      <c r="S11" s="6"/>
+      <c r="S11" s="6">
+        <v>772.9</v>
+      </c>
       <c r="T11" s="6"/>
       <c r="U11" s="6"/>
       <c r="V11" s="6"/>
@@ -1387,7 +1413,9 @@
       <c r="M12" s="6">
         <v>1033.8</v>
       </c>
-      <c r="N12" s="6"/>
+      <c r="N12" s="6">
+        <v>948.4</v>
+      </c>
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
       <c r="Q12" s="6">
@@ -1396,7 +1424,9 @@
       <c r="R12" s="6">
         <v>2916.3999999999996</v>
       </c>
-      <c r="S12" s="6"/>
+      <c r="S12" s="6">
+        <v>3357.5</v>
+      </c>
       <c r="T12" s="6"/>
       <c r="U12" s="6"/>
       <c r="V12" s="6"/>
@@ -1458,7 +1488,9 @@
       <c r="M13" s="6">
         <v>722.5</v>
       </c>
-      <c r="N13" s="6"/>
+      <c r="N13" s="6">
+        <v>1152.7</v>
+      </c>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
       <c r="Q13" s="6">
@@ -1467,7 +1499,9 @@
       <c r="R13" s="6">
         <v>2259.6</v>
       </c>
-      <c r="S13" s="6"/>
+      <c r="S13" s="6">
+        <v>3208.7</v>
+      </c>
       <c r="T13" s="6"/>
       <c r="U13" s="6"/>
       <c r="V13" s="6"/>
@@ -1529,7 +1563,9 @@
       <c r="M14" s="6">
         <v>683.3</v>
       </c>
-      <c r="N14" s="6"/>
+      <c r="N14" s="6">
+        <v>999.8</v>
+      </c>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6">
@@ -1538,7 +1574,9 @@
       <c r="R14" s="6">
         <v>2189.1</v>
       </c>
-      <c r="S14" s="6"/>
+      <c r="S14" s="6">
+        <v>2855.8</v>
+      </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6"/>
       <c r="V14" s="6"/>
@@ -1600,7 +1638,9 @@
       <c r="M15" s="6">
         <v>723.5</v>
       </c>
-      <c r="N15" s="6"/>
+      <c r="N15" s="6">
+        <v>764.1</v>
+      </c>
       <c r="O15" s="6"/>
       <c r="P15" s="6"/>
       <c r="Q15" s="6">
@@ -1609,7 +1649,9 @@
       <c r="R15" s="6">
         <v>1834.1</v>
       </c>
-      <c r="S15" s="6"/>
+      <c r="S15" s="6">
+        <v>2403.6999999999998</v>
+      </c>
       <c r="T15" s="6"/>
       <c r="U15" s="6"/>
       <c r="V15" s="6"/>
@@ -1671,7 +1713,9 @@
       <c r="M16" s="6">
         <v>349.5</v>
       </c>
-      <c r="N16" s="6"/>
+      <c r="N16" s="6">
+        <v>337.2</v>
+      </c>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
       <c r="Q16" s="6">
@@ -1680,7 +1724,9 @@
       <c r="R16" s="6">
         <v>1052.8</v>
       </c>
-      <c r="S16" s="6"/>
+      <c r="S16" s="6">
+        <v>1306.7</v>
+      </c>
       <c r="T16" s="6"/>
       <c r="U16" s="6"/>
       <c r="V16" s="6"/>
@@ -1742,7 +1788,9 @@
       <c r="M17" s="8">
         <v>1756.3</v>
       </c>
-      <c r="N17" s="6"/>
+      <c r="N17" s="8">
+        <v>2101.1</v>
+      </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="8">
@@ -1751,7 +1799,9 @@
       <c r="R17" s="8">
         <v>5175.6000000000004</v>
       </c>
-      <c r="S17" s="6"/>
+      <c r="S17" s="8">
+        <v>6566.2</v>
+      </c>
       <c r="T17" s="6"/>
       <c r="U17" s="6"/>
       <c r="V17" s="6"/>
@@ -1811,7 +1861,9 @@
       <c r="M18" s="6">
         <v>758.1</v>
       </c>
-      <c r="N18" s="6"/>
+      <c r="N18" s="6">
+        <v>889</v>
+      </c>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
       <c r="Q18" s="6">
@@ -1820,7 +1872,9 @@
       <c r="R18" s="6">
         <v>2311.4</v>
       </c>
-      <c r="S18" s="6"/>
+      <c r="S18" s="6">
+        <v>2781.9</v>
+      </c>
       <c r="T18" s="6"/>
       <c r="U18" s="6"/>
       <c r="V18" s="6"/>
@@ -1876,7 +1930,7 @@
         <v>747.3</v>
       </c>
       <c r="J19" s="6">
-        <f t="shared" ref="J19:M19" si="7">+J17-J18</f>
+        <f t="shared" ref="J19:N19" si="7">+J17-J18</f>
         <v>917.5</v>
       </c>
       <c r="K19" s="6">
@@ -1891,7 +1945,10 @@
         <f t="shared" si="7"/>
         <v>998.19999999999993</v>
       </c>
-      <c r="N19" s="6"/>
+      <c r="N19" s="6">
+        <f t="shared" si="7"/>
+        <v>1212.0999999999999</v>
+      </c>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
       <c r="Q19" s="6">
@@ -1902,7 +1959,10 @@
         <f>+R17-R18</f>
         <v>2864.2000000000003</v>
       </c>
-      <c r="S19" s="6"/>
+      <c r="S19" s="6">
+        <f>+S17-S18</f>
+        <v>3784.2999999999997</v>
+      </c>
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
@@ -1962,7 +2022,9 @@
       <c r="M20" s="6">
         <v>776.6</v>
       </c>
-      <c r="N20" s="6"/>
+      <c r="N20" s="6">
+        <v>988.3</v>
+      </c>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
       <c r="Q20" s="6">
@@ -1971,7 +2033,9 @@
       <c r="R20" s="6">
         <v>2422.8000000000002</v>
       </c>
-      <c r="S20" s="6"/>
+      <c r="S20" s="6">
+        <v>3104.6</v>
+      </c>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
@@ -2031,7 +2095,9 @@
       <c r="M21" s="6">
         <v>10.199999999999999</v>
       </c>
-      <c r="N21" s="6"/>
+      <c r="N21" s="6">
+        <v>0.9</v>
+      </c>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
       <c r="Q21" s="6">
@@ -2040,7 +2106,9 @@
       <c r="R21" s="6">
         <v>1.9</v>
       </c>
-      <c r="S21" s="6"/>
+      <c r="S21" s="6">
+        <v>14</v>
+      </c>
       <c r="T21" s="6"/>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
@@ -2100,7 +2168,9 @@
       <c r="M22" s="6">
         <v>4.5</v>
       </c>
-      <c r="N22" s="6"/>
+      <c r="N22" s="6">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6">
@@ -2109,7 +2179,9 @@
       <c r="R22" s="6">
         <v>31.3</v>
       </c>
-      <c r="S22" s="6"/>
+      <c r="S22" s="6">
+        <v>36.1</v>
+      </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
@@ -2165,7 +2237,7 @@
         <v>176.69999999999996</v>
       </c>
       <c r="J23" s="6">
-        <f t="shared" ref="J23:M23" si="10">+J19-J20-J21+J22</f>
+        <f t="shared" ref="J23:N23" si="10">+J19-J20-J21+J22</f>
         <v>193.60000000000005</v>
       </c>
       <c r="K23" s="6">
@@ -2180,7 +2252,10 @@
         <f t="shared" si="10"/>
         <v>215.89999999999992</v>
       </c>
-      <c r="N23" s="6"/>
+      <c r="N23" s="6">
+        <f t="shared" si="10"/>
+        <v>227.99999999999994</v>
+      </c>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
       <c r="Q23" s="6">
@@ -2191,7 +2266,10 @@
         <f>+R19-R20-R21+R22</f>
         <v>470.80000000000013</v>
       </c>
-      <c r="S23" s="6"/>
+      <c r="S23" s="6">
+        <f>+S19-S20-S21+S22</f>
+        <v>701.79999999999984</v>
+      </c>
       <c r="T23" s="6"/>
       <c r="U23" s="6"/>
       <c r="V23" s="6"/>
@@ -2253,7 +2331,9 @@
       <c r="M24" s="6">
         <v>-25.6</v>
       </c>
-      <c r="N24" s="6"/>
+      <c r="N24" s="6">
+        <v>2</v>
+      </c>
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
       <c r="Q24" s="6">
@@ -2264,7 +2344,9 @@
         <f t="shared" ref="R24" si="13">+SUM(G24:J24)</f>
         <v>-5.2000000000000011</v>
       </c>
-      <c r="S24" s="6"/>
+      <c r="S24" s="6">
+        <v>6.4</v>
+      </c>
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
       <c r="V24" s="6"/>
@@ -2324,7 +2406,9 @@
       <c r="M25" s="6">
         <v>-5.9</v>
       </c>
-      <c r="N25" s="6"/>
+      <c r="N25" s="6">
+        <v>20.100000000000001</v>
+      </c>
       <c r="O25" s="6"/>
       <c r="P25" s="6"/>
       <c r="Q25" s="6">
@@ -2333,7 +2417,9 @@
       <c r="R25" s="6">
         <v>229</v>
       </c>
-      <c r="S25" s="6"/>
+      <c r="S25" s="6">
+        <v>97.7</v>
+      </c>
       <c r="T25" s="6"/>
       <c r="U25" s="6"/>
       <c r="V25" s="6"/>
@@ -2394,7 +2480,9 @@
       <c r="M26" s="6">
         <v>-1.5</v>
       </c>
-      <c r="N26" s="6"/>
+      <c r="N26" s="6">
+        <v>2.5</v>
+      </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
       <c r="Q26" s="6">
@@ -2403,7 +2491,9 @@
       <c r="R26" s="6">
         <v>75.400000000000006</v>
       </c>
-      <c r="S26" s="6"/>
+      <c r="S26" s="6">
+        <v>-14</v>
+      </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
       <c r="V26" s="6"/>
@@ -2459,7 +2549,7 @@
         <v>128.89999999999995</v>
       </c>
       <c r="J27" s="6">
-        <f t="shared" ref="J27:M27" si="16">+J23+J24-J25-J26</f>
+        <f t="shared" ref="J27:N27" si="16">+J23+J24-J25-J26</f>
         <v>70.900000000000063</v>
       </c>
       <c r="K27" s="6">
@@ -2474,10 +2564,13 @@
         <f t="shared" si="16"/>
         <v>197.69999999999993</v>
       </c>
-      <c r="N27" s="6"/>
+      <c r="N27" s="6">
+        <f t="shared" si="16"/>
+        <v>207.39999999999995</v>
+      </c>
       <c r="O27" s="6"/>
       <c r="P27" s="6">
-        <f t="shared" ref="P27:R27" si="17">+P23+P24-P25-P26</f>
+        <f t="shared" ref="P27:S27" si="17">+P23+P24-P25-P26</f>
         <v>0</v>
       </c>
       <c r="Q27" s="6">
@@ -2488,7 +2581,10 @@
         <f t="shared" si="17"/>
         <v>161.20000000000013</v>
       </c>
-      <c r="S27" s="6"/>
+      <c r="S27" s="6">
+        <f t="shared" si="17"/>
+        <v>624.49999999999977</v>
+      </c>
       <c r="T27" s="6"/>
       <c r="U27" s="6"/>
       <c r="V27" s="6"/>
@@ -2548,7 +2644,9 @@
       <c r="M28" s="6">
         <v>51.3</v>
       </c>
-      <c r="N28" s="6"/>
+      <c r="N28" s="6">
+        <v>73.900000000000006</v>
+      </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
       <c r="Q28" s="6">
@@ -2557,7 +2655,9 @@
       <c r="R28" s="6">
         <v>82.8</v>
       </c>
-      <c r="S28" s="6"/>
+      <c r="S28" s="6">
+        <v>184.1</v>
+      </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
@@ -2613,7 +2713,7 @@
         <v>56.199999999999946</v>
       </c>
       <c r="J29" s="6">
-        <f t="shared" ref="J29:M29" si="20">+J27-J28</f>
+        <f t="shared" ref="J29:N29" si="20">+J27-J28</f>
         <v>17.100000000000065</v>
       </c>
       <c r="K29" s="6">
@@ -2628,10 +2728,13 @@
         <f t="shared" si="20"/>
         <v>146.39999999999992</v>
       </c>
-      <c r="N29" s="6"/>
+      <c r="N29" s="6">
+        <f t="shared" si="20"/>
+        <v>133.49999999999994</v>
+      </c>
       <c r="O29" s="6"/>
       <c r="P29" s="6">
-        <f t="shared" ref="P29:R29" si="21">+P27-P28</f>
+        <f t="shared" ref="P29:S29" si="21">+P27-P28</f>
         <v>0</v>
       </c>
       <c r="Q29" s="6">
@@ -2642,7 +2745,10 @@
         <f t="shared" si="21"/>
         <v>78.400000000000134</v>
       </c>
-      <c r="S29" s="6"/>
+      <c r="S29" s="6">
+        <f t="shared" si="21"/>
+        <v>440.39999999999975</v>
+      </c>
       <c r="T29" s="6"/>
       <c r="U29" s="6"/>
       <c r="V29" s="6"/>
@@ -2702,7 +2808,9 @@
       <c r="M30" s="6">
         <v>3.3</v>
       </c>
-      <c r="N30" s="6"/>
+      <c r="N30" s="6">
+        <v>2</v>
+      </c>
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
       <c r="Q30" s="6">
@@ -2711,7 +2819,9 @@
       <c r="R30" s="6">
         <v>5.8000000000000007</v>
       </c>
-      <c r="S30" s="6"/>
+      <c r="S30" s="6">
+        <v>13</v>
+      </c>
       <c r="T30" s="6"/>
       <c r="U30" s="6"/>
       <c r="V30" s="6"/>
@@ -2782,10 +2892,13 @@
         <f>+M29-M30</f>
         <v>143.09999999999991</v>
       </c>
-      <c r="N31" s="6"/>
+      <c r="N31" s="6">
+        <f>+N29-N30</f>
+        <v>131.49999999999994</v>
+      </c>
       <c r="O31" s="6"/>
       <c r="P31" s="6">
-        <f t="shared" ref="P31:R31" si="23">+P29-P30</f>
+        <f t="shared" ref="P31:S31" si="23">+P29-P30</f>
         <v>0</v>
       </c>
       <c r="Q31" s="6">
@@ -2796,7 +2909,10 @@
         <f t="shared" si="23"/>
         <v>72.600000000000136</v>
       </c>
-      <c r="S31" s="6"/>
+      <c r="S31" s="6">
+        <f t="shared" si="23"/>
+        <v>427.39999999999975</v>
+      </c>
       <c r="T31" s="6"/>
       <c r="U31" s="6"/>
       <c r="V31" s="6"/>
@@ -2892,7 +3008,7 @@
         <v>0.1104048258068074</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" ref="J33:M33" si="25">+J31/J34</f>
+        <f t="shared" ref="J33:N33" si="25">+J31/J34</f>
         <v>2.9669793367748994E-2</v>
       </c>
       <c r="K33" s="9">
@@ -2907,7 +3023,10 @@
         <f t="shared" si="25"/>
         <v>0.25728183001534388</v>
       </c>
-      <c r="N33" s="6"/>
+      <c r="N33" s="9">
+        <f t="shared" si="25"/>
+        <v>0.23616971048355681</v>
+      </c>
       <c r="O33" s="6"/>
       <c r="P33" s="9" t="e">
         <f t="shared" ref="P33:S33" si="26">+P31/P34</f>
@@ -2921,9 +3040,9 @@
         <f t="shared" si="26"/>
         <v>0.14570037888405196</v>
       </c>
-      <c r="S33" s="9" t="e">
+      <c r="S33" s="9">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
+        <v>0.76924913584650645</v>
       </c>
       <c r="T33" s="6"/>
       <c r="U33" s="6"/>
@@ -2984,7 +3103,9 @@
       <c r="M34" s="6">
         <v>556.19940199999996</v>
       </c>
-      <c r="N34" s="6"/>
+      <c r="N34" s="6">
+        <v>556.80298600000003</v>
+      </c>
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
       <c r="Q34" s="6">
@@ -2993,7 +3114,9 @@
       <c r="R34" s="6">
         <v>498.28284975000003</v>
       </c>
-      <c r="S34" s="6"/>
+      <c r="S34" s="6">
+        <v>555.60673399999996</v>
+      </c>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
       <c r="V34" s="6"/>
@@ -3092,12 +3215,24 @@
         <f>+M8/I8-1</f>
         <v>0.23193473193473202</v>
       </c>
-      <c r="N36" s="7"/>
+      <c r="N36" s="10">
+        <f>+N8/J8-1</f>
+        <v>2.0191649555099334E-2</v>
+      </c>
       <c r="O36" s="7"/>
       <c r="P36" s="7"/>
-      <c r="Q36" s="7"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="7"/>
+      <c r="Q36" s="14" t="e">
+        <f t="shared" ref="Q36:S36" si="28">+Q8/P8-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R36" s="14">
+        <f t="shared" si="28"/>
+        <v>6.5057364546720509E-2</v>
+      </c>
+      <c r="S36" s="14">
+        <f>+S8/R8-1</f>
+        <v>0.12440846824408469</v>
+      </c>
       <c r="T36" s="7"/>
       <c r="U36" s="7"/>
       <c r="V36" s="7"/>
@@ -3137,31 +3272,43 @@
         <v>5.464480874316946E-3</v>
       </c>
       <c r="I37" s="10">
-        <f t="shared" ref="I37:M39" si="28">+I9/E9-1</f>
+        <f t="shared" ref="I37:N39" si="29">+I9/E9-1</f>
         <v>7.2527472527472492E-2</v>
       </c>
       <c r="J37" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>8.0510338759348876E-2</v>
       </c>
       <c r="K37" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.12002892263195952</v>
       </c>
       <c r="L37" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>7.4456521739130421E-2</v>
       </c>
       <c r="M37" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.17663934426229511</v>
       </c>
-      <c r="N37" s="7"/>
+      <c r="N37" s="10">
+        <f t="shared" si="29"/>
+        <v>0.40736970684039076</v>
+      </c>
       <c r="O37" s="7"/>
       <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
-      <c r="R37" s="7"/>
-      <c r="S37" s="7"/>
+      <c r="Q37" s="14" t="e">
+        <f t="shared" ref="Q37:S37" si="30">+Q9/P9-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R37" s="14">
+        <f t="shared" si="30"/>
+        <v>4.5384432842904721E-2</v>
+      </c>
+      <c r="S37" s="14">
+        <f>+S9/R9-1</f>
+        <v>0.20628795187560289</v>
+      </c>
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
@@ -3201,31 +3348,43 @@
         <v>0.5372340425531914</v>
       </c>
       <c r="I38" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.56499999999999995</v>
       </c>
       <c r="J38" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.5386773547094188</v>
       </c>
       <c r="K38" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.43132220795892162</v>
       </c>
       <c r="L38" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.41937716262975777</v>
       </c>
       <c r="M38" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.47444089456868999</v>
       </c>
-      <c r="N38" s="7"/>
+      <c r="N38" s="10">
+        <f t="shared" si="29"/>
+        <v>0.4175566553790051</v>
+      </c>
       <c r="O38" s="7"/>
       <c r="P38" s="7"/>
-      <c r="Q38" s="7"/>
-      <c r="R38" s="7"/>
-      <c r="S38" s="7"/>
+      <c r="Q38" s="14" t="e">
+        <f t="shared" ref="Q38:S38" si="31">+Q10/P10-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R38" s="14">
+        <f t="shared" si="31"/>
+        <v>0.5400593471810089</v>
+      </c>
+      <c r="S38" s="14">
+        <f>+S10/R10-1</f>
+        <v>0.43499036608863206</v>
+      </c>
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
       <c r="V38" s="7"/>
@@ -3265,31 +3424,43 @@
         <v>0.45205479452054798</v>
       </c>
       <c r="I39" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.47058823529411775</v>
       </c>
       <c r="J39" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.52380952380952372</v>
       </c>
       <c r="K39" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.4886148007590132</v>
       </c>
       <c r="L39" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.45754716981132071</v>
       </c>
       <c r="M39" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.53679999999999994</v>
       </c>
-      <c r="N39" s="7"/>
+      <c r="N39" s="10">
+        <f t="shared" si="29"/>
+        <v>0.53068181818181803</v>
+      </c>
       <c r="O39" s="7"/>
       <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="7"/>
+      <c r="Q39" s="14" t="e">
+        <f t="shared" ref="Q39:S39" si="32">+Q11/P11-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R39" s="14">
+        <f t="shared" si="32"/>
+        <v>0.45775248933143664</v>
+      </c>
+      <c r="S39" s="14">
+        <f>+S11/R11-1</f>
+        <v>0.50839188134270108</v>
+      </c>
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
@@ -3321,11 +3492,11 @@
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="10">
-        <f t="shared" ref="G40:H43" si="29">+G14/C14-1</f>
+        <f t="shared" ref="G40:H43" si="33">+G14/C14-1</f>
         <v>0.45661971830985926</v>
       </c>
       <c r="H40" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0.34323432343234317</v>
       </c>
       <c r="I40" s="10">
@@ -3348,12 +3519,24 @@
         <f>+M14/I14-1</f>
         <v>0.31403846153846149</v>
       </c>
-      <c r="N40" s="7"/>
+      <c r="N40" s="10">
+        <f>+N14/J14-1</f>
+        <v>0.34201342281879188</v>
+      </c>
       <c r="O40" s="7"/>
       <c r="P40" s="7"/>
-      <c r="Q40" s="7"/>
-      <c r="R40" s="7"/>
-      <c r="S40" s="7"/>
+      <c r="Q40" s="14" t="e">
+        <f t="shared" ref="Q40:S40" si="34">+Q14/P14-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R40" s="14">
+        <f t="shared" si="34"/>
+        <v>0.36273655378486036</v>
+      </c>
+      <c r="S40" s="14">
+        <f>+S14/R14-1</f>
+        <v>0.30455438307980454</v>
+      </c>
       <c r="T40" s="7"/>
       <c r="U40" s="7"/>
       <c r="V40" s="7"/>
@@ -3385,39 +3568,51 @@
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>6.5782493368700345E-2</v>
       </c>
       <c r="H41" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0.10948905109489049</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" ref="I41:M43" si="30">+I15/E15-1</f>
+        <f t="shared" ref="I41:N43" si="35">+I15/E15-1</f>
         <v>7.8787878787878851E-2</v>
       </c>
       <c r="J41" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.13070776255707739</v>
       </c>
       <c r="K41" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.25037332005973112</v>
       </c>
       <c r="L41" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.36085526315789473</v>
       </c>
       <c r="M41" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.35486891385767794</v>
       </c>
-      <c r="N41" s="7"/>
+      <c r="N41" s="10">
+        <f t="shared" si="35"/>
+        <v>0.28571428571428581</v>
+      </c>
       <c r="O41" s="7"/>
       <c r="P41" s="7"/>
-      <c r="Q41" s="7"/>
-      <c r="R41" s="7"/>
-      <c r="S41" s="7"/>
+      <c r="Q41" s="14" t="e">
+        <f t="shared" ref="Q41:S41" si="36">+Q15/P15-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R41" s="14">
+        <f t="shared" si="36"/>
+        <v>9.7212251734864807E-2</v>
+      </c>
+      <c r="S41" s="14">
+        <f>+S15/R15-1</f>
+        <v>0.31056103811133529</v>
+      </c>
       <c r="T41" s="7"/>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
@@ -3449,39 +3644,51 @@
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>-0.13962264150943393</v>
       </c>
       <c r="H42" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>1.0714285714285676E-2</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>-0.2592592592592593</v>
       </c>
       <c r="J42" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.22144329896907222</v>
       </c>
       <c r="K42" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.11951754385964897</v>
       </c>
       <c r="L42" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.1084805653710248</v>
       </c>
       <c r="M42" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.74750000000000005</v>
       </c>
-      <c r="N42" s="7"/>
+      <c r="N42" s="10">
+        <f t="shared" si="35"/>
+        <v>0.13841998649561105</v>
+      </c>
       <c r="O42" s="7"/>
       <c r="P42" s="7"/>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="7"/>
+      <c r="Q42" s="14" t="e">
+        <f t="shared" ref="Q42:S42" si="37">+Q16/P16-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R42" s="14">
+        <f t="shared" si="37"/>
+        <v>-5.1958577217469659E-2</v>
+      </c>
+      <c r="S42" s="14">
+        <f>+S16/R16-1</f>
+        <v>0.24116641337386024</v>
+      </c>
       <c r="T42" s="7"/>
       <c r="U42" s="7"/>
       <c r="V42" s="7"/>
@@ -3513,39 +3720,51 @@
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0.13538988860325629</v>
       </c>
       <c r="H43" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0.15989729225023352</v>
       </c>
       <c r="I43" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.17405255398491026</v>
       </c>
       <c r="J43" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.23201506591337107</v>
       </c>
       <c r="K43" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.23480083857442358</v>
       </c>
       <c r="L43" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.24401287985510156</v>
       </c>
       <c r="M43" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>0.29731127197518092</v>
       </c>
-      <c r="N43" s="7"/>
+      <c r="N43" s="12">
+        <f t="shared" si="35"/>
+        <v>0.28468358300213992</v>
+      </c>
       <c r="O43" s="7"/>
       <c r="P43" s="7"/>
-      <c r="Q43" s="7"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="7"/>
+      <c r="Q43" s="12" t="e">
+        <f t="shared" ref="Q43:S43" si="38">+Q17/P17-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R43" s="12">
+        <f t="shared" si="38"/>
+        <v>0.17957016204389564</v>
+      </c>
+      <c r="S43" s="12">
+        <f>+S17/R17-1</f>
+        <v>0.26868382409768898</v>
+      </c>
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
@@ -3573,27 +3792,27 @@
         <v>52</v>
       </c>
       <c r="C44" s="10">
-        <f t="shared" ref="C44:H44" si="31">+C19/C17</f>
+        <f t="shared" ref="C44:H44" si="39">+C19/C17</f>
         <v>0.52832524040750262</v>
       </c>
       <c r="D44" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0.53291316526610644</v>
       </c>
       <c r="E44" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0.51010320006937815</v>
       </c>
       <c r="F44" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0.52406779661016956</v>
       </c>
       <c r="G44" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0.5434800838574424</v>
       </c>
       <c r="H44" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0.55473938418192792</v>
       </c>
       <c r="I44" s="10">
@@ -3616,12 +3835,27 @@
         <f>+M19/M17</f>
         <v>0.56835392586687916</v>
       </c>
-      <c r="N44" s="7"/>
+      <c r="N44" s="10">
+        <f>+N19/N17</f>
+        <v>0.5768882966065394</v>
+      </c>
       <c r="O44" s="7"/>
-      <c r="P44" s="7"/>
-      <c r="Q44" s="7"/>
-      <c r="R44" s="7"/>
-      <c r="S44" s="7"/>
+      <c r="P44" s="10" t="e">
+        <f t="shared" ref="P44:S44" si="40">+P19/P17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q44" s="10">
+        <f t="shared" ref="Q44:S44" si="41">+Q19/Q17</f>
+        <v>0.52314424413701932</v>
+      </c>
+      <c r="R44" s="10">
+        <f t="shared" si="41"/>
+        <v>0.55340443620063373</v>
+      </c>
+      <c r="S44" s="10">
+        <f t="shared" si="40"/>
+        <v>0.57633029758459986</v>
+      </c>
       <c r="T44" s="7"/>
       <c r="U44" s="7"/>
       <c r="V44" s="7"/>
@@ -3649,27 +3883,27 @@
         <v>53</v>
       </c>
       <c r="C45" s="10">
-        <f t="shared" ref="C45:H45" si="32">+C23/C17</f>
+        <f t="shared" ref="C45:H45" si="42">+C23/C17</f>
         <v>0.12415500333238121</v>
       </c>
       <c r="D45" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="42"/>
         <v>8.7535014005601722E-3</v>
       </c>
       <c r="E45" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="42"/>
         <v>9.0798716503338761E-2</v>
       </c>
       <c r="F45" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="42"/>
         <v>4.5047080979284407E-2</v>
       </c>
       <c r="G45" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="42"/>
         <v>9.1404612159329199E-2</v>
       </c>
       <c r="H45" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="42"/>
         <v>-8.5530287784263345E-3</v>
       </c>
       <c r="I45" s="10">
@@ -3692,12 +3926,27 @@
         <f>+M23/M17</f>
         <v>0.12292888458691563</v>
       </c>
-      <c r="N45" s="7"/>
+      <c r="N45" s="10">
+        <f>+N23/N17</f>
+        <v>0.10851458759697299</v>
+      </c>
       <c r="O45" s="7"/>
-      <c r="P45" s="7"/>
-      <c r="Q45" s="7"/>
-      <c r="R45" s="7"/>
-      <c r="S45" s="7"/>
+      <c r="P45" s="10" t="e">
+        <f t="shared" ref="P45:S45" si="43">+P23/P17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q45" s="10">
+        <f t="shared" ref="Q45:S45" si="44">+Q23/Q17</f>
+        <v>6.891993527360564E-2</v>
+      </c>
+      <c r="R45" s="10">
+        <f t="shared" si="44"/>
+        <v>9.0965298709328402E-2</v>
+      </c>
+      <c r="S45" s="10">
+        <f t="shared" si="43"/>
+        <v>0.10688069202887512</v>
+      </c>
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
       <c r="V45" s="7"/>
@@ -3725,27 +3974,27 @@
         <v>54</v>
       </c>
       <c r="C46" s="10">
-        <f t="shared" ref="C46:H46" si="33">+C28/C27</f>
+        <f t="shared" ref="C46:H46" si="45">+C28/C27</f>
         <v>0.58333333333333348</v>
       </c>
       <c r="D46" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>-5.6644880174291916E-2</v>
       </c>
       <c r="E46" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>-9.878787878787632</v>
       </c>
       <c r="F46" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>-0.72363636363636419</v>
       </c>
       <c r="G46" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>0.54304635761589126</v>
       </c>
       <c r="H46" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>0.96648044692737256</v>
       </c>
       <c r="I46" s="10">
@@ -3768,12 +4017,27 @@
         <f>+M28/M27</f>
         <v>0.25948406676783015</v>
       </c>
-      <c r="N46" s="7"/>
+      <c r="N46" s="10">
+        <f>+N28/N27</f>
+        <v>0.35631629701060763</v>
+      </c>
       <c r="O46" s="7"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="7"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="7"/>
+      <c r="P46" s="10" t="e">
+        <f t="shared" ref="P46:S46" si="46">+P28/P27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q46" s="10">
+        <f t="shared" ref="Q46:S46" si="47">+Q28/Q27</f>
+        <v>-0.99712918660286554</v>
+      </c>
+      <c r="R46" s="10">
+        <f t="shared" si="47"/>
+        <v>0.51364764267990026</v>
+      </c>
+      <c r="S46" s="10">
+        <f t="shared" si="46"/>
+        <v>0.29479583666933556</v>
+      </c>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
       <c r="V46" s="7"/>

--- a/AS.xlsx
+++ b/AS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D75A897-FEE2-4E1B-981C-3B97BE1CC67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EBEF13-7B35-4B8D-9E88-4D8955824805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{53BA411E-2A41-4FEC-A342-AE8C41391E29}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{53BA411E-2A41-4FEC-A342-AE8C41391E29}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
   <si>
     <t>Amer Sports</t>
   </si>
@@ -242,6 +242,18 @@
   <si>
     <t>FY25</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -252,13 +264,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -321,31 +339,32 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -702,7 +721,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>40.49</v>
+        <v>35.26</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -710,10 +729,10 @@
         <v>3</v>
       </c>
       <c r="J3" s="6">
-        <v>556.80298600000003</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>60</v>
+        <v>564.90232900000001</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -725,7 +744,7 @@
       </c>
       <c r="J4" s="7">
         <f>+J2*J3</f>
-        <v>22544.952903140002</v>
+        <v>19918.456120539999</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -736,10 +755,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="7">
-        <v>652.29999999999995</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>60</v>
+        <v>683.7</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -747,11 +766,10 @@
         <v>6</v>
       </c>
       <c r="J6" s="7">
-        <f>792.3+142.8</f>
-        <v>935.09999999999991</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>60</v>
+        <v>144.9</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -760,7 +778,7 @@
       </c>
       <c r="J7" s="7">
         <f>+J4-J5+J6</f>
-        <v>22827.752903140001</v>
+        <v>19379.656120539999</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -783,7 +801,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC70E52E-A4D2-4CB7-BF9B-AFB47E0B1996}">
-  <dimension ref="A1:AP252"/>
+  <dimension ref="A1:AT252"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -791,12 +809,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:46" x14ac:dyDescent="0.2">
       <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
@@ -833,20 +851,32 @@
       <c r="N2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="O2" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>61</v>
       </c>
@@ -883,20 +913,28 @@
       <c r="M3" s="3">
         <v>275</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="Q3" s="2">
+      <c r="N3" s="2">
+        <v>288</v>
+      </c>
+      <c r="O3" s="3">
+        <v>297</v>
+      </c>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="U3" s="2">
         <f>+F3</f>
         <v>187</v>
       </c>
-      <c r="R3" s="2">
+      <c r="V3" s="2">
         <f>+J3</f>
         <v>223</v>
       </c>
-      <c r="S3" s="2">
+      <c r="W3" s="2">
         <v>288</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>42</v>
       </c>
@@ -933,20 +971,28 @@
       <c r="M4" s="3">
         <v>285</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="Q4" s="2">
-        <f t="shared" ref="Q4:Q5" si="0">+F4</f>
+      <c r="N4" s="2">
+        <v>331</v>
+      </c>
+      <c r="O4" s="3">
+        <v>340</v>
+      </c>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="U4" s="2">
+        <f t="shared" ref="U4:U5" si="0">+F4</f>
         <v>126</v>
       </c>
-      <c r="R4" s="2">
-        <f t="shared" ref="R4:R5" si="1">+J4</f>
+      <c r="V4" s="2">
+        <f t="shared" ref="V4:V5" si="1">+J4</f>
         <v>229</v>
       </c>
-      <c r="S4" s="2">
+      <c r="W4" s="2">
         <v>331</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>62</v>
       </c>
@@ -983,20 +1029,28 @@
       <c r="M5" s="3">
         <v>71</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="Q5" s="2">
+      <c r="N5" s="2">
+        <v>84</v>
+      </c>
+      <c r="O5" s="3">
+        <v>85</v>
+      </c>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="U5" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="R5" s="2">
+      <c r="V5" s="2">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="S5" s="2">
+      <c r="W5" s="2">
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
         <v>63</v>
       </c>
@@ -1009,7 +1063,7 @@
         <v>299</v>
       </c>
       <c r="E6" s="5">
-        <f t="shared" ref="E6:M6" si="3">+SUM(E3:E5)</f>
+        <f t="shared" ref="E6:O6" si="3">+SUM(E3:E5)</f>
         <v>301</v>
       </c>
       <c r="F6" s="5">
@@ -1044,25 +1098,35 @@
         <f t="shared" si="3"/>
         <v>631</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="P6" s="4">
-        <f t="shared" ref="P6:Q6" si="4">+SUM(P3:P5)</f>
+      <c r="N6" s="5">
+        <f t="shared" si="3"/>
+        <v>703</v>
+      </c>
+      <c r="O6" s="5">
+        <f t="shared" si="3"/>
+        <v>722</v>
+      </c>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="T6" s="4">
+        <f t="shared" ref="T6:U6" si="4">+SUM(T3:T5)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="U6" s="4">
         <f t="shared" si="4"/>
         <v>325</v>
       </c>
-      <c r="R6" s="4">
-        <f>+SUM(R3:R5)</f>
+      <c r="V6" s="4">
+        <f>+SUM(V3:V5)</f>
         <v>505</v>
       </c>
-      <c r="S6" s="4">
-        <f>+SUM(S3:S5)</f>
+      <c r="W6" s="4">
+        <f>+SUM(W3:W5)</f>
         <v>703</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.2">
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -1075,8 +1139,12 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
@@ -1116,28 +1184,30 @@
       <c r="N8" s="6">
         <v>596.20000000000005</v>
       </c>
-      <c r="O8" s="6"/>
+      <c r="O8" s="6">
+        <v>644.5</v>
+      </c>
       <c r="P8" s="6"/>
-      <c r="Q8" s="6">
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6">
         <v>1507.9</v>
       </c>
-      <c r="R8" s="6">
+      <c r="V8" s="6">
         <v>1606</v>
       </c>
-      <c r="S8" s="6">
+      <c r="W8" s="6">
         <v>1805.8</v>
       </c>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
       <c r="X8" s="6"/>
       <c r="Y8" s="6"/>
       <c r="Z8" s="6"/>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="7"/>
-      <c r="AC8" s="7"/>
-      <c r="AD8" s="7"/>
+      <c r="AA8" s="6"/>
+      <c r="AB8" s="6"/>
+      <c r="AC8" s="6"/>
+      <c r="AD8" s="6"/>
       <c r="AE8" s="7"/>
       <c r="AF8" s="7"/>
       <c r="AG8" s="7"/>
@@ -1150,8 +1220,12 @@
       <c r="AN8" s="7"/>
       <c r="AO8" s="7"/>
       <c r="AP8" s="7"/>
-    </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ8" s="7"/>
+      <c r="AR8" s="7"/>
+      <c r="AS8" s="7"/>
+      <c r="AT8" s="7"/>
+    </row>
+    <row r="9" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
@@ -1191,28 +1265,30 @@
       <c r="N9" s="6">
         <v>691.3</v>
       </c>
-      <c r="O9" s="6"/>
+      <c r="O9" s="6">
+        <v>548.79999999999995</v>
+      </c>
       <c r="P9" s="6"/>
-      <c r="Q9" s="6">
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6">
         <v>1685.6</v>
       </c>
-      <c r="R9" s="6">
+      <c r="V9" s="6">
         <v>1762.1000000000001</v>
       </c>
-      <c r="S9" s="6">
+      <c r="W9" s="6">
         <v>2125.6</v>
       </c>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
       <c r="Z9" s="6"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
-      <c r="AC9" s="7"/>
-      <c r="AD9" s="7"/>
+      <c r="AA9" s="6"/>
+      <c r="AB9" s="6"/>
+      <c r="AC9" s="6"/>
+      <c r="AD9" s="6"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
       <c r="AG9" s="7"/>
@@ -1225,8 +1301,12 @@
       <c r="AN9" s="7"/>
       <c r="AO9" s="7"/>
       <c r="AP9" s="7"/>
-    </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ9" s="7"/>
+      <c r="AR9" s="7"/>
+      <c r="AS9" s="7"/>
+      <c r="AT9" s="7"/>
+    </row>
+    <row r="10" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>37</v>
       </c>
@@ -1266,28 +1346,30 @@
       <c r="N10" s="6">
         <v>544.20000000000005</v>
       </c>
-      <c r="O10" s="6"/>
+      <c r="O10" s="6">
+        <v>512.79999999999995</v>
+      </c>
       <c r="P10" s="6"/>
-      <c r="Q10" s="6">
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6">
         <v>842.5</v>
       </c>
-      <c r="R10" s="6">
+      <c r="V10" s="6">
         <v>1297.5</v>
       </c>
-      <c r="S10" s="6">
+      <c r="W10" s="6">
         <v>1861.9</v>
       </c>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
       <c r="X10" s="6"/>
       <c r="Y10" s="6"/>
       <c r="Z10" s="6"/>
-      <c r="AA10" s="7"/>
-      <c r="AB10" s="7"/>
-      <c r="AC10" s="7"/>
-      <c r="AD10" s="7"/>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
       <c r="AE10" s="7"/>
       <c r="AF10" s="7"/>
       <c r="AG10" s="7"/>
@@ -1300,8 +1382,12 @@
       <c r="AN10" s="7"/>
       <c r="AO10" s="7"/>
       <c r="AP10" s="7"/>
-    </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ10" s="7"/>
+      <c r="AR10" s="7"/>
+      <c r="AS10" s="7"/>
+      <c r="AT10" s="7"/>
+    </row>
+    <row r="11" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>38</v>
       </c>
@@ -1341,28 +1427,30 @@
       <c r="N11" s="6">
         <v>269.39999999999998</v>
       </c>
-      <c r="O11" s="6"/>
+      <c r="O11" s="6">
+        <v>239.4</v>
+      </c>
       <c r="P11" s="6"/>
-      <c r="Q11" s="6">
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6">
         <v>351.5</v>
       </c>
-      <c r="R11" s="6">
+      <c r="V11" s="6">
         <v>512.4</v>
       </c>
-      <c r="S11" s="6">
+      <c r="W11" s="6">
         <v>772.9</v>
       </c>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
       <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
       <c r="Z11" s="6"/>
-      <c r="AA11" s="7"/>
-      <c r="AB11" s="7"/>
-      <c r="AC11" s="7"/>
-      <c r="AD11" s="7"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
       <c r="AE11" s="7"/>
       <c r="AF11" s="7"/>
       <c r="AG11" s="7"/>
@@ -1375,8 +1463,12 @@
       <c r="AN11" s="7"/>
       <c r="AO11" s="7"/>
       <c r="AP11" s="7"/>
-    </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ11" s="7"/>
+      <c r="AR11" s="7"/>
+      <c r="AS11" s="7"/>
+      <c r="AT11" s="7"/>
+    </row>
+    <row r="12" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>39</v>
       </c>
@@ -1416,28 +1508,30 @@
       <c r="N12" s="6">
         <v>948.4</v>
       </c>
-      <c r="O12" s="6"/>
+      <c r="O12" s="6">
+        <v>944</v>
+      </c>
       <c r="P12" s="6"/>
-      <c r="Q12" s="6">
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6">
         <v>2809.5</v>
       </c>
-      <c r="R12" s="6">
+      <c r="V12" s="6">
         <v>2916.3999999999996</v>
       </c>
-      <c r="S12" s="6">
+      <c r="W12" s="6">
         <v>3357.5</v>
       </c>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
       <c r="X12" s="6"/>
       <c r="Y12" s="6"/>
       <c r="Z12" s="6"/>
-      <c r="AA12" s="7"/>
-      <c r="AB12" s="7"/>
-      <c r="AC12" s="7"/>
-      <c r="AD12" s="7"/>
+      <c r="AA12" s="6"/>
+      <c r="AB12" s="6"/>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="7"/>
       <c r="AG12" s="7"/>
@@ -1450,8 +1544,12 @@
       <c r="AN12" s="7"/>
       <c r="AO12" s="7"/>
       <c r="AP12" s="7"/>
-    </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ12" s="7"/>
+      <c r="AR12" s="7"/>
+      <c r="AS12" s="7"/>
+      <c r="AT12" s="7"/>
+    </row>
+    <row r="13" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>40</v>
       </c>
@@ -1491,28 +1589,30 @@
       <c r="N13" s="6">
         <v>1152.7</v>
       </c>
-      <c r="O13" s="6"/>
+      <c r="O13" s="15">
+        <v>1001.5</v>
+      </c>
       <c r="P13" s="6"/>
-      <c r="Q13" s="6">
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6">
         <v>1578</v>
       </c>
-      <c r="R13" s="6">
+      <c r="V13" s="6">
         <v>2259.6</v>
       </c>
-      <c r="S13" s="6">
+      <c r="W13" s="6">
         <v>3208.7</v>
       </c>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
       <c r="X13" s="6"/>
       <c r="Y13" s="6"/>
       <c r="Z13" s="6"/>
-      <c r="AA13" s="7"/>
-      <c r="AB13" s="7"/>
-      <c r="AC13" s="7"/>
-      <c r="AD13" s="7"/>
+      <c r="AA13" s="6"/>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="6"/>
+      <c r="AD13" s="6"/>
       <c r="AE13" s="7"/>
       <c r="AF13" s="7"/>
       <c r="AG13" s="7"/>
@@ -1525,8 +1625,12 @@
       <c r="AN13" s="7"/>
       <c r="AO13" s="7"/>
       <c r="AP13" s="7"/>
-    </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ13" s="7"/>
+      <c r="AR13" s="7"/>
+      <c r="AS13" s="7"/>
+      <c r="AT13" s="7"/>
+    </row>
+    <row r="14" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>41</v>
       </c>
@@ -1566,28 +1670,30 @@
       <c r="N14" s="6">
         <v>999.8</v>
       </c>
-      <c r="O14" s="6"/>
+      <c r="O14" s="6">
+        <v>885</v>
+      </c>
       <c r="P14" s="6"/>
-      <c r="Q14" s="6">
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6">
         <v>1606.4</v>
       </c>
-      <c r="R14" s="6">
+      <c r="V14" s="6">
         <v>2189.1</v>
       </c>
-      <c r="S14" s="6">
+      <c r="W14" s="6">
         <v>2855.8</v>
       </c>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
       <c r="X14" s="6"/>
       <c r="Y14" s="6"/>
       <c r="Z14" s="6"/>
-      <c r="AA14" s="7"/>
-      <c r="AB14" s="7"/>
-      <c r="AC14" s="7"/>
-      <c r="AD14" s="7"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
       <c r="AG14" s="7"/>
@@ -1600,8 +1706,12 @@
       <c r="AN14" s="7"/>
       <c r="AO14" s="7"/>
       <c r="AP14" s="7"/>
-    </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ14" s="7"/>
+      <c r="AR14" s="7"/>
+      <c r="AS14" s="7"/>
+      <c r="AT14" s="7"/>
+    </row>
+    <row r="15" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
@@ -1641,28 +1751,30 @@
       <c r="N15" s="6">
         <v>764.1</v>
       </c>
-      <c r="O15" s="6"/>
+      <c r="O15" s="6">
+        <v>713.6</v>
+      </c>
       <c r="P15" s="6"/>
-      <c r="Q15" s="6">
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6">
         <v>1671.6</v>
       </c>
-      <c r="R15" s="6">
+      <c r="V15" s="6">
         <v>1834.1</v>
       </c>
-      <c r="S15" s="6">
+      <c r="W15" s="6">
         <v>2403.6999999999998</v>
       </c>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
       <c r="X15" s="6"/>
       <c r="Y15" s="6"/>
       <c r="Z15" s="6"/>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="7"/>
-      <c r="AC15" s="7"/>
-      <c r="AD15" s="7"/>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="6"/>
+      <c r="AD15" s="6"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="7"/>
       <c r="AG15" s="7"/>
@@ -1675,8 +1787,12 @@
       <c r="AN15" s="7"/>
       <c r="AO15" s="7"/>
       <c r="AP15" s="7"/>
-    </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ15" s="7"/>
+      <c r="AR15" s="7"/>
+      <c r="AS15" s="7"/>
+      <c r="AT15" s="7"/>
+    </row>
+    <row r="16" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>43</v>
       </c>
@@ -1716,28 +1832,30 @@
       <c r="N16" s="6">
         <v>337.2</v>
       </c>
-      <c r="O16" s="6"/>
+      <c r="O16" s="6">
+        <v>346.9</v>
+      </c>
       <c r="P16" s="6"/>
-      <c r="Q16" s="6">
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6">
         <v>1110.5</v>
       </c>
-      <c r="R16" s="6">
+      <c r="V16" s="6">
         <v>1052.8</v>
       </c>
-      <c r="S16" s="6">
+      <c r="W16" s="6">
         <v>1306.7</v>
       </c>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-      <c r="V16" s="6"/>
-      <c r="W16" s="6"/>
       <c r="X16" s="6"/>
       <c r="Y16" s="6"/>
       <c r="Z16" s="6"/>
-      <c r="AA16" s="7"/>
-      <c r="AB16" s="7"/>
-      <c r="AC16" s="7"/>
-      <c r="AD16" s="7"/>
+      <c r="AA16" s="6"/>
+      <c r="AB16" s="6"/>
+      <c r="AC16" s="6"/>
+      <c r="AD16" s="6"/>
       <c r="AE16" s="7"/>
       <c r="AF16" s="7"/>
       <c r="AG16" s="7"/>
@@ -1750,8 +1868,12 @@
       <c r="AN16" s="7"/>
       <c r="AO16" s="7"/>
       <c r="AP16" s="7"/>
-    </row>
-    <row r="17" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AQ16" s="7"/>
+      <c r="AR16" s="7"/>
+      <c r="AS16" s="7"/>
+      <c r="AT16" s="7"/>
+    </row>
+    <row r="17" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B17" s="4" t="s">
         <v>19</v>
       </c>
@@ -1791,28 +1913,30 @@
       <c r="N17" s="8">
         <v>2101.1</v>
       </c>
-      <c r="O17" s="8"/>
+      <c r="O17" s="8">
+        <v>1945.5</v>
+      </c>
       <c r="P17" s="8"/>
-      <c r="Q17" s="8">
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8">
         <v>4387.7</v>
       </c>
-      <c r="R17" s="8">
+      <c r="V17" s="8">
         <v>5175.6000000000004</v>
       </c>
-      <c r="S17" s="8">
+      <c r="W17" s="8">
         <v>6566.2</v>
       </c>
-      <c r="T17" s="6"/>
-      <c r="U17" s="6"/>
-      <c r="V17" s="6"/>
-      <c r="W17" s="6"/>
       <c r="X17" s="6"/>
       <c r="Y17" s="6"/>
       <c r="Z17" s="6"/>
-      <c r="AA17" s="7"/>
-      <c r="AB17" s="7"/>
-      <c r="AC17" s="7"/>
-      <c r="AD17" s="7"/>
+      <c r="AA17" s="6"/>
+      <c r="AB17" s="6"/>
+      <c r="AC17" s="6"/>
+      <c r="AD17" s="6"/>
       <c r="AE17" s="7"/>
       <c r="AF17" s="7"/>
       <c r="AG17" s="7"/>
@@ -1823,8 +1947,12 @@
       <c r="AL17" s="7"/>
       <c r="AM17" s="7"/>
       <c r="AN17" s="7"/>
-    </row>
-    <row r="18" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO17" s="7"/>
+      <c r="AP17" s="7"/>
+      <c r="AQ17" s="7"/>
+      <c r="AR17" s="7"/>
+    </row>
+    <row r="18" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>20</v>
       </c>
@@ -1864,28 +1992,30 @@
       <c r="N18" s="6">
         <v>889</v>
       </c>
-      <c r="O18" s="6"/>
+      <c r="O18" s="6">
+        <v>780.1</v>
+      </c>
       <c r="P18" s="6"/>
-      <c r="Q18" s="6">
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6">
         <v>2092.3000000000002</v>
       </c>
-      <c r="R18" s="6">
+      <c r="V18" s="6">
         <v>2311.4</v>
       </c>
-      <c r="S18" s="6">
+      <c r="W18" s="6">
         <v>2781.9</v>
       </c>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
       <c r="X18" s="6"/>
       <c r="Y18" s="6"/>
       <c r="Z18" s="6"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="7"/>
-      <c r="AD18" s="7"/>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="6"/>
+      <c r="AD18" s="6"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="7"/>
       <c r="AG18" s="7"/>
@@ -1896,8 +2026,12 @@
       <c r="AL18" s="7"/>
       <c r="AM18" s="7"/>
       <c r="AN18" s="7"/>
-    </row>
-    <row r="19" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO18" s="7"/>
+      <c r="AP18" s="7"/>
+      <c r="AQ18" s="7"/>
+      <c r="AR18" s="7"/>
+    </row>
+    <row r="19" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
@@ -1930,7 +2064,7 @@
         <v>747.3</v>
       </c>
       <c r="J19" s="6">
-        <f t="shared" ref="J19:N19" si="7">+J17-J18</f>
+        <f t="shared" ref="J19:O19" si="7">+J17-J18</f>
         <v>917.5</v>
       </c>
       <c r="K19" s="6">
@@ -1949,31 +2083,34 @@
         <f t="shared" si="7"/>
         <v>1212.0999999999999</v>
       </c>
-      <c r="O19" s="6"/>
+      <c r="O19" s="6">
+        <f t="shared" si="7"/>
+        <v>1165.4000000000001</v>
+      </c>
       <c r="P19" s="6"/>
-      <c r="Q19" s="6">
-        <f>+Q17-Q18</f>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="6"/>
+      <c r="T19" s="6"/>
+      <c r="U19" s="6">
+        <f>+U17-U18</f>
         <v>2295.3999999999996</v>
       </c>
-      <c r="R19" s="6">
-        <f>+R17-R18</f>
+      <c r="V19" s="6">
+        <f>+V17-V18</f>
         <v>2864.2000000000003</v>
       </c>
-      <c r="S19" s="6">
-        <f>+S17-S18</f>
+      <c r="W19" s="6">
+        <f>+W17-W18</f>
         <v>3784.2999999999997</v>
       </c>
-      <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="6"/>
       <c r="X19" s="6"/>
       <c r="Y19" s="6"/>
       <c r="Z19" s="6"/>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="7"/>
-      <c r="AC19" s="7"/>
-      <c r="AD19" s="7"/>
+      <c r="AA19" s="6"/>
+      <c r="AB19" s="6"/>
+      <c r="AC19" s="6"/>
+      <c r="AD19" s="6"/>
       <c r="AE19" s="7"/>
       <c r="AF19" s="7"/>
       <c r="AG19" s="7"/>
@@ -1984,8 +2121,12 @@
       <c r="AL19" s="7"/>
       <c r="AM19" s="7"/>
       <c r="AN19" s="7"/>
-    </row>
-    <row r="20" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO19" s="7"/>
+      <c r="AP19" s="7"/>
+      <c r="AQ19" s="7"/>
+      <c r="AR19" s="7"/>
+    </row>
+    <row r="20" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>22</v>
       </c>
@@ -2025,28 +2166,30 @@
       <c r="N20" s="6">
         <v>988.3</v>
       </c>
-      <c r="O20" s="6"/>
+      <c r="O20" s="6">
+        <v>856.2</v>
+      </c>
       <c r="P20" s="6"/>
-      <c r="Q20" s="6">
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="6">
         <v>2001.8000000000002</v>
       </c>
-      <c r="R20" s="6">
+      <c r="V20" s="6">
         <v>2422.8000000000002</v>
       </c>
-      <c r="S20" s="6">
+      <c r="W20" s="6">
         <v>3104.6</v>
       </c>
-      <c r="T20" s="6"/>
-      <c r="U20" s="6"/>
-      <c r="V20" s="6"/>
-      <c r="W20" s="6"/>
       <c r="X20" s="6"/>
       <c r="Y20" s="6"/>
       <c r="Z20" s="6"/>
-      <c r="AA20" s="7"/>
-      <c r="AB20" s="7"/>
-      <c r="AC20" s="7"/>
-      <c r="AD20" s="7"/>
+      <c r="AA20" s="6"/>
+      <c r="AB20" s="6"/>
+      <c r="AC20" s="6"/>
+      <c r="AD20" s="6"/>
       <c r="AE20" s="7"/>
       <c r="AF20" s="7"/>
       <c r="AG20" s="7"/>
@@ -2057,8 +2200,12 @@
       <c r="AL20" s="7"/>
       <c r="AM20" s="7"/>
       <c r="AN20" s="7"/>
-    </row>
-    <row r="21" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO20" s="7"/>
+      <c r="AP20" s="7"/>
+      <c r="AQ20" s="7"/>
+      <c r="AR20" s="7"/>
+    </row>
+    <row r="21" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>23</v>
       </c>
@@ -2098,28 +2245,30 @@
       <c r="N21" s="6">
         <v>0.9</v>
       </c>
-      <c r="O21" s="6"/>
+      <c r="O21" s="6">
+        <v>0.7</v>
+      </c>
       <c r="P21" s="6"/>
-      <c r="Q21" s="6">
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="6"/>
+      <c r="U21" s="6">
         <v>2.3999999999999995</v>
       </c>
-      <c r="R21" s="6">
+      <c r="V21" s="6">
         <v>1.9</v>
       </c>
-      <c r="S21" s="6">
+      <c r="W21" s="6">
         <v>14</v>
       </c>
-      <c r="T21" s="6"/>
-      <c r="U21" s="6"/>
-      <c r="V21" s="6"/>
-      <c r="W21" s="6"/>
       <c r="X21" s="6"/>
       <c r="Y21" s="6"/>
       <c r="Z21" s="6"/>
-      <c r="AA21" s="7"/>
-      <c r="AB21" s="7"/>
-      <c r="AC21" s="7"/>
-      <c r="AD21" s="7"/>
+      <c r="AA21" s="6"/>
+      <c r="AB21" s="6"/>
+      <c r="AC21" s="6"/>
+      <c r="AD21" s="6"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="7"/>
       <c r="AG21" s="7"/>
@@ -2130,8 +2279,12 @@
       <c r="AL21" s="7"/>
       <c r="AM21" s="7"/>
       <c r="AN21" s="7"/>
-    </row>
-    <row r="22" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO21" s="7"/>
+      <c r="AP21" s="7"/>
+      <c r="AQ21" s="7"/>
+      <c r="AR21" s="7"/>
+    </row>
+    <row r="22" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>31</v>
       </c>
@@ -2171,28 +2324,30 @@
       <c r="N22" s="6">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O22" s="6"/>
+      <c r="O22" s="6">
+        <v>12.6</v>
+      </c>
       <c r="P22" s="6"/>
-      <c r="Q22" s="6">
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6">
         <v>11.2</v>
       </c>
-      <c r="R22" s="6">
+      <c r="V22" s="6">
         <v>31.3</v>
       </c>
-      <c r="S22" s="6">
+      <c r="W22" s="6">
         <v>36.1</v>
       </c>
-      <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
-      <c r="V22" s="6"/>
-      <c r="W22" s="6"/>
       <c r="X22" s="6"/>
       <c r="Y22" s="6"/>
       <c r="Z22" s="6"/>
-      <c r="AA22" s="7"/>
-      <c r="AB22" s="7"/>
-      <c r="AC22" s="7"/>
-      <c r="AD22" s="7"/>
+      <c r="AA22" s="6"/>
+      <c r="AB22" s="6"/>
+      <c r="AC22" s="6"/>
+      <c r="AD22" s="6"/>
       <c r="AE22" s="7"/>
       <c r="AF22" s="7"/>
       <c r="AG22" s="7"/>
@@ -2203,8 +2358,12 @@
       <c r="AL22" s="7"/>
       <c r="AM22" s="7"/>
       <c r="AN22" s="7"/>
-    </row>
-    <row r="23" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO22" s="7"/>
+      <c r="AP22" s="7"/>
+      <c r="AQ22" s="7"/>
+      <c r="AR22" s="7"/>
+    </row>
+    <row r="23" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>32</v>
       </c>
@@ -2237,7 +2396,7 @@
         <v>176.69999999999996</v>
       </c>
       <c r="J23" s="6">
-        <f t="shared" ref="J23:N23" si="10">+J19-J20-J21+J22</f>
+        <f t="shared" ref="J23:O23" si="10">+J19-J20-J21+J22</f>
         <v>193.60000000000005</v>
       </c>
       <c r="K23" s="6">
@@ -2256,31 +2415,34 @@
         <f t="shared" si="10"/>
         <v>227.99999999999994</v>
       </c>
-      <c r="O23" s="6"/>
+      <c r="O23" s="6">
+        <f t="shared" si="10"/>
+        <v>321.10000000000008</v>
+      </c>
       <c r="P23" s="6"/>
-      <c r="Q23" s="6">
-        <f t="shared" ref="Q23" si="11">+Q19-Q20-Q21+Q22</f>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6">
+        <f t="shared" ref="U23" si="11">+U19-U20-U21+U22</f>
         <v>302.39999999999947</v>
       </c>
-      <c r="R23" s="6">
-        <f>+R19-R20-R21+R22</f>
+      <c r="V23" s="6">
+        <f>+V19-V20-V21+V22</f>
         <v>470.80000000000013</v>
       </c>
-      <c r="S23" s="6">
-        <f>+S19-S20-S21+S22</f>
+      <c r="W23" s="6">
+        <f>+W19-W20-W21+W22</f>
         <v>701.79999999999984</v>
       </c>
-      <c r="T23" s="6"/>
-      <c r="U23" s="6"/>
-      <c r="V23" s="6"/>
-      <c r="W23" s="6"/>
       <c r="X23" s="6"/>
       <c r="Y23" s="6"/>
       <c r="Z23" s="6"/>
-      <c r="AA23" s="7"/>
-      <c r="AB23" s="7"/>
-      <c r="AC23" s="7"/>
-      <c r="AD23" s="7"/>
+      <c r="AA23" s="6"/>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6"/>
       <c r="AE23" s="7"/>
       <c r="AF23" s="7"/>
       <c r="AG23" s="7"/>
@@ -2291,8 +2453,12 @@
       <c r="AL23" s="7"/>
       <c r="AM23" s="7"/>
       <c r="AN23" s="7"/>
-    </row>
-    <row r="24" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO23" s="7"/>
+      <c r="AP23" s="7"/>
+      <c r="AQ23" s="7"/>
+      <c r="AR23" s="7"/>
+    </row>
+    <row r="24" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>24</v>
       </c>
@@ -2334,30 +2500,32 @@
       <c r="N24" s="6">
         <v>2</v>
       </c>
-      <c r="O24" s="6"/>
+      <c r="O24" s="6">
+        <v>2.7</v>
+      </c>
       <c r="P24" s="6"/>
-      <c r="Q24" s="6">
-        <f t="shared" ref="Q24" si="12">+SUM(C24:F24)</f>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="6">
+        <f t="shared" ref="U24" si="12">+SUM(C24:F24)</f>
         <v>6.4</v>
       </c>
-      <c r="R24" s="6">
-        <f t="shared" ref="R24" si="13">+SUM(G24:J24)</f>
+      <c r="V24" s="6">
+        <f t="shared" ref="V24" si="13">+SUM(G24:J24)</f>
         <v>-5.2000000000000011</v>
       </c>
-      <c r="S24" s="6">
+      <c r="W24" s="6">
         <v>6.4</v>
       </c>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
       <c r="X24" s="6"/>
       <c r="Y24" s="6"/>
       <c r="Z24" s="6"/>
-      <c r="AA24" s="7"/>
-      <c r="AB24" s="7"/>
-      <c r="AC24" s="7"/>
-      <c r="AD24" s="7"/>
+      <c r="AA24" s="6"/>
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="6"/>
+      <c r="AD24" s="6"/>
       <c r="AE24" s="7"/>
       <c r="AF24" s="7"/>
       <c r="AG24" s="7"/>
@@ -2368,8 +2536,12 @@
       <c r="AL24" s="7"/>
       <c r="AM24" s="7"/>
       <c r="AN24" s="7"/>
-    </row>
-    <row r="25" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO24" s="7"/>
+      <c r="AP24" s="7"/>
+      <c r="AQ24" s="7"/>
+      <c r="AR24" s="7"/>
+    </row>
+    <row r="25" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>25</v>
       </c>
@@ -2409,28 +2581,31 @@
       <c r="N25" s="6">
         <v>20.100000000000001</v>
       </c>
-      <c r="O25" s="6"/>
+      <c r="O25" s="6">
+        <f>24.9+7.8</f>
+        <v>32.699999999999996</v>
+      </c>
       <c r="P25" s="6"/>
-      <c r="Q25" s="6">
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6">
         <v>406</v>
       </c>
-      <c r="R25" s="6">
+      <c r="V25" s="6">
         <v>229</v>
       </c>
-      <c r="S25" s="6">
+      <c r="W25" s="6">
         <v>97.7</v>
       </c>
-      <c r="T25" s="6"/>
-      <c r="U25" s="6"/>
-      <c r="V25" s="6"/>
-      <c r="W25" s="6"/>
       <c r="X25" s="6"/>
       <c r="Y25" s="6"/>
       <c r="Z25" s="6"/>
-      <c r="AA25" s="7"/>
-      <c r="AB25" s="7"/>
-      <c r="AC25" s="7"/>
-      <c r="AD25" s="7"/>
+      <c r="AA25" s="6"/>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="6"/>
+      <c r="AD25" s="6"/>
       <c r="AE25" s="7"/>
       <c r="AF25" s="7"/>
       <c r="AG25" s="7"/>
@@ -2441,8 +2616,12 @@
       <c r="AL25" s="7"/>
       <c r="AM25" s="7"/>
       <c r="AN25" s="7"/>
-    </row>
-    <row r="26" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO25" s="7"/>
+      <c r="AP25" s="7"/>
+      <c r="AQ25" s="7"/>
+      <c r="AR25" s="7"/>
+    </row>
+    <row r="26" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>26</v>
       </c>
@@ -2483,28 +2662,30 @@
       <c r="N26" s="6">
         <v>2.5</v>
       </c>
-      <c r="O26" s="6"/>
+      <c r="O26" s="6">
+        <v>50.5</v>
+      </c>
       <c r="P26" s="6"/>
-      <c r="Q26" s="6">
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6"/>
+      <c r="U26" s="6">
         <v>7.3</v>
       </c>
-      <c r="R26" s="6">
+      <c r="V26" s="6">
         <v>75.400000000000006</v>
       </c>
-      <c r="S26" s="6">
+      <c r="W26" s="6">
         <v>-14</v>
       </c>
-      <c r="T26" s="6"/>
-      <c r="U26" s="6"/>
-      <c r="V26" s="6"/>
-      <c r="W26" s="6"/>
       <c r="X26" s="6"/>
       <c r="Y26" s="6"/>
       <c r="Z26" s="6"/>
-      <c r="AA26" s="7"/>
-      <c r="AB26" s="7"/>
-      <c r="AC26" s="7"/>
-      <c r="AD26" s="7"/>
+      <c r="AA26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="6"/>
+      <c r="AD26" s="6"/>
       <c r="AE26" s="7"/>
       <c r="AF26" s="7"/>
       <c r="AG26" s="7"/>
@@ -2515,8 +2696,12 @@
       <c r="AL26" s="7"/>
       <c r="AM26" s="7"/>
       <c r="AN26" s="7"/>
-    </row>
-    <row r="27" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO26" s="7"/>
+      <c r="AP26" s="7"/>
+      <c r="AQ26" s="7"/>
+      <c r="AR26" s="7"/>
+    </row>
+    <row r="27" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>27</v>
       </c>
@@ -2549,7 +2734,7 @@
         <v>128.89999999999995</v>
       </c>
       <c r="J27" s="6">
-        <f t="shared" ref="J27:N27" si="16">+J23+J24-J25-J26</f>
+        <f t="shared" ref="J27:O27" si="16">+J23+J24-J25-J26</f>
         <v>70.900000000000063</v>
       </c>
       <c r="K27" s="6">
@@ -2568,34 +2753,37 @@
         <f t="shared" si="16"/>
         <v>207.39999999999995</v>
       </c>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6">
-        <f t="shared" ref="P27:S27" si="17">+P23+P24-P25-P26</f>
+      <c r="O27" s="6">
+        <f t="shared" si="16"/>
+        <v>240.60000000000008</v>
+      </c>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="6"/>
+      <c r="T27" s="6">
+        <f t="shared" ref="T27:W27" si="17">+T23+T24-T25-T26</f>
         <v>0</v>
       </c>
-      <c r="Q27" s="6">
+      <c r="U27" s="6">
         <f t="shared" si="17"/>
         <v>-104.50000000000055</v>
       </c>
-      <c r="R27" s="6">
+      <c r="V27" s="6">
         <f t="shared" si="17"/>
         <v>161.20000000000013</v>
       </c>
-      <c r="S27" s="6">
+      <c r="W27" s="6">
         <f t="shared" si="17"/>
         <v>624.49999999999977</v>
       </c>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
       <c r="X27" s="6"/>
       <c r="Y27" s="6"/>
       <c r="Z27" s="6"/>
-      <c r="AA27" s="7"/>
-      <c r="AB27" s="7"/>
-      <c r="AC27" s="7"/>
-      <c r="AD27" s="7"/>
+      <c r="AA27" s="6"/>
+      <c r="AB27" s="6"/>
+      <c r="AC27" s="6"/>
+      <c r="AD27" s="6"/>
       <c r="AE27" s="7"/>
       <c r="AF27" s="7"/>
       <c r="AG27" s="7"/>
@@ -2606,8 +2794,12 @@
       <c r="AL27" s="7"/>
       <c r="AM27" s="7"/>
       <c r="AN27" s="7"/>
-    </row>
-    <row r="28" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO27" s="7"/>
+      <c r="AP27" s="7"/>
+      <c r="AQ27" s="7"/>
+      <c r="AR27" s="7"/>
+    </row>
+    <row r="28" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>28</v>
       </c>
@@ -2647,28 +2839,30 @@
       <c r="N28" s="6">
         <v>73.900000000000006</v>
       </c>
-      <c r="O28" s="6"/>
+      <c r="O28" s="6">
+        <v>70.5</v>
+      </c>
       <c r="P28" s="6"/>
-      <c r="Q28" s="6">
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="6"/>
+      <c r="T28" s="6"/>
+      <c r="U28" s="6">
         <v>104.2</v>
       </c>
-      <c r="R28" s="6">
+      <c r="V28" s="6">
         <v>82.8</v>
       </c>
-      <c r="S28" s="6">
+      <c r="W28" s="6">
         <v>184.1</v>
       </c>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
       <c r="X28" s="6"/>
       <c r="Y28" s="6"/>
       <c r="Z28" s="6"/>
-      <c r="AA28" s="7"/>
-      <c r="AB28" s="7"/>
-      <c r="AC28" s="7"/>
-      <c r="AD28" s="7"/>
+      <c r="AA28" s="6"/>
+      <c r="AB28" s="6"/>
+      <c r="AC28" s="6"/>
+      <c r="AD28" s="6"/>
       <c r="AE28" s="7"/>
       <c r="AF28" s="7"/>
       <c r="AG28" s="7"/>
@@ -2679,8 +2873,12 @@
       <c r="AL28" s="7"/>
       <c r="AM28" s="7"/>
       <c r="AN28" s="7"/>
-    </row>
-    <row r="29" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO28" s="7"/>
+      <c r="AP28" s="7"/>
+      <c r="AQ28" s="7"/>
+      <c r="AR28" s="7"/>
+    </row>
+    <row r="29" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>29</v>
       </c>
@@ -2713,7 +2911,7 @@
         <v>56.199999999999946</v>
       </c>
       <c r="J29" s="6">
-        <f t="shared" ref="J29:N29" si="20">+J27-J28</f>
+        <f t="shared" ref="J29:O29" si="20">+J27-J28</f>
         <v>17.100000000000065</v>
       </c>
       <c r="K29" s="6">
@@ -2732,34 +2930,37 @@
         <f t="shared" si="20"/>
         <v>133.49999999999994</v>
       </c>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6">
-        <f t="shared" ref="P29:S29" si="21">+P27-P28</f>
+      <c r="O29" s="6">
+        <f t="shared" si="20"/>
+        <v>170.10000000000008</v>
+      </c>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="6"/>
+      <c r="T29" s="6">
+        <f t="shared" ref="T29:W29" si="21">+T27-T28</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="6">
+      <c r="U29" s="6">
         <f t="shared" si="21"/>
         <v>-208.70000000000056</v>
       </c>
-      <c r="R29" s="6">
+      <c r="V29" s="6">
         <f t="shared" si="21"/>
         <v>78.400000000000134</v>
       </c>
-      <c r="S29" s="6">
+      <c r="W29" s="6">
         <f t="shared" si="21"/>
         <v>440.39999999999975</v>
       </c>
-      <c r="T29" s="6"/>
-      <c r="U29" s="6"/>
-      <c r="V29" s="6"/>
-      <c r="W29" s="6"/>
       <c r="X29" s="6"/>
       <c r="Y29" s="6"/>
       <c r="Z29" s="6"/>
-      <c r="AA29" s="7"/>
-      <c r="AB29" s="7"/>
-      <c r="AC29" s="7"/>
-      <c r="AD29" s="7"/>
+      <c r="AA29" s="6"/>
+      <c r="AB29" s="6"/>
+      <c r="AC29" s="6"/>
+      <c r="AD29" s="6"/>
       <c r="AE29" s="7"/>
       <c r="AF29" s="7"/>
       <c r="AG29" s="7"/>
@@ -2770,8 +2971,12 @@
       <c r="AL29" s="7"/>
       <c r="AM29" s="7"/>
       <c r="AN29" s="7"/>
-    </row>
-    <row r="30" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO29" s="7"/>
+      <c r="AP29" s="7"/>
+      <c r="AQ29" s="7"/>
+      <c r="AR29" s="7"/>
+    </row>
+    <row r="30" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>33</v>
       </c>
@@ -2811,28 +3016,30 @@
       <c r="N30" s="6">
         <v>2</v>
       </c>
-      <c r="O30" s="6"/>
+      <c r="O30" s="6">
+        <v>5.5</v>
+      </c>
       <c r="P30" s="6"/>
-      <c r="Q30" s="6">
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6">
         <v>-0.19999999999999996</v>
       </c>
-      <c r="R30" s="6">
+      <c r="V30" s="6">
         <v>5.8000000000000007</v>
       </c>
-      <c r="S30" s="6">
+      <c r="W30" s="6">
         <v>13</v>
       </c>
-      <c r="T30" s="6"/>
-      <c r="U30" s="6"/>
-      <c r="V30" s="6"/>
-      <c r="W30" s="6"/>
       <c r="X30" s="6"/>
       <c r="Y30" s="6"/>
       <c r="Z30" s="6"/>
-      <c r="AA30" s="7"/>
-      <c r="AB30" s="7"/>
-      <c r="AC30" s="7"/>
-      <c r="AD30" s="7"/>
+      <c r="AA30" s="6"/>
+      <c r="AB30" s="6"/>
+      <c r="AC30" s="6"/>
+      <c r="AD30" s="6"/>
       <c r="AE30" s="7"/>
       <c r="AF30" s="7"/>
       <c r="AG30" s="7"/>
@@ -2843,8 +3050,12 @@
       <c r="AL30" s="7"/>
       <c r="AM30" s="7"/>
       <c r="AN30" s="7"/>
-    </row>
-    <row r="31" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO30" s="7"/>
+      <c r="AP30" s="7"/>
+      <c r="AQ30" s="7"/>
+      <c r="AR30" s="7"/>
+    </row>
+    <row r="31" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>34</v>
       </c>
@@ -2873,57 +3084,60 @@
         <v>-3.7000000000000965</v>
       </c>
       <c r="I31" s="6">
-        <f>+I29-I30</f>
+        <f t="shared" ref="I31:O31" si="23">+I29-I30</f>
         <v>55.799999999999947</v>
       </c>
       <c r="J31" s="6">
-        <f>+J29-J30</f>
+        <f t="shared" si="23"/>
         <v>15.400000000000066</v>
       </c>
       <c r="K31" s="6">
-        <f>+K29-K30</f>
+        <f t="shared" si="23"/>
         <v>134.60000000000005</v>
       </c>
       <c r="L31" s="6">
-        <f>+L29-L30</f>
+        <f t="shared" si="23"/>
         <v>18.200000000000021</v>
       </c>
       <c r="M31" s="6">
-        <f>+M29-M30</f>
+        <f t="shared" si="23"/>
         <v>143.09999999999991</v>
       </c>
       <c r="N31" s="6">
-        <f>+N29-N30</f>
+        <f t="shared" si="23"/>
         <v>131.49999999999994</v>
       </c>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6">
-        <f t="shared" ref="P31:S31" si="23">+P29-P30</f>
+      <c r="O31" s="6">
+        <f t="shared" si="23"/>
+        <v>164.60000000000008</v>
+      </c>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="6"/>
+      <c r="T31" s="6">
+        <f t="shared" ref="T31:W31" si="24">+T29-T30</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="6">
-        <f t="shared" si="23"/>
+      <c r="U31" s="6">
+        <f t="shared" si="24"/>
         <v>-208.50000000000057</v>
       </c>
-      <c r="R31" s="6">
-        <f t="shared" si="23"/>
+      <c r="V31" s="6">
+        <f t="shared" si="24"/>
         <v>72.600000000000136</v>
       </c>
-      <c r="S31" s="6">
-        <f t="shared" si="23"/>
+      <c r="W31" s="6">
+        <f t="shared" si="24"/>
         <v>427.39999999999975</v>
       </c>
-      <c r="T31" s="6"/>
-      <c r="U31" s="6"/>
-      <c r="V31" s="6"/>
-      <c r="W31" s="6"/>
       <c r="X31" s="6"/>
       <c r="Y31" s="6"/>
       <c r="Z31" s="6"/>
-      <c r="AA31" s="7"/>
-      <c r="AB31" s="7"/>
-      <c r="AC31" s="7"/>
-      <c r="AD31" s="7"/>
+      <c r="AA31" s="6"/>
+      <c r="AB31" s="6"/>
+      <c r="AC31" s="6"/>
+      <c r="AD31" s="6"/>
       <c r="AE31" s="7"/>
       <c r="AF31" s="7"/>
       <c r="AG31" s="7"/>
@@ -2934,8 +3148,12 @@
       <c r="AL31" s="7"/>
       <c r="AM31" s="7"/>
       <c r="AN31" s="7"/>
-    </row>
-    <row r="32" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO31" s="7"/>
+      <c r="AP31" s="7"/>
+      <c r="AQ31" s="7"/>
+      <c r="AR31" s="7"/>
+    </row>
+    <row r="32" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -2960,10 +3178,10 @@
       <c r="X32" s="6"/>
       <c r="Y32" s="6"/>
       <c r="Z32" s="6"/>
-      <c r="AA32" s="7"/>
-      <c r="AB32" s="7"/>
-      <c r="AC32" s="7"/>
-      <c r="AD32" s="7"/>
+      <c r="AA32" s="6"/>
+      <c r="AB32" s="6"/>
+      <c r="AC32" s="6"/>
+      <c r="AD32" s="6"/>
       <c r="AE32" s="7"/>
       <c r="AF32" s="7"/>
       <c r="AG32" s="7"/>
@@ -2974,33 +3192,37 @@
       <c r="AL32" s="7"/>
       <c r="AM32" s="7"/>
       <c r="AN32" s="7"/>
-    </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO32" s="7"/>
+      <c r="AP32" s="7"/>
+      <c r="AQ32" s="7"/>
+      <c r="AR32" s="7"/>
+    </row>
+    <row r="33" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C33" s="9">
-        <f t="shared" ref="C33:H33" si="24">+C31/C34</f>
+        <f t="shared" ref="C33:H33" si="25">+C31/C34</f>
         <v>4.9414874954605587E-2</v>
       </c>
       <c r="D33" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.25201586226848871</v>
       </c>
       <c r="E33" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-9.8049515041507121E-2</v>
       </c>
       <c r="F33" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.24161273069909781</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1.1005072015432781E-2</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-7.3231130687452396E-3</v>
       </c>
       <c r="I33" s="9">
@@ -3008,53 +3230,56 @@
         <v>0.1104048258068074</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" ref="J33:N33" si="25">+J31/J34</f>
+        <f t="shared" ref="J33:O33" si="26">+J31/J34</f>
         <v>2.9669793367748994E-2</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.24296635945911133</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>3.2769120911237702E-2</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.25728183001534388</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.23616971048355681</v>
       </c>
-      <c r="O33" s="6"/>
-      <c r="P33" s="9" t="e">
-        <f t="shared" ref="P33:S33" si="26">+P31/P34</f>
+      <c r="O33" s="9">
+        <f t="shared" si="26"/>
+        <v>0.29137780382562395</v>
+      </c>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="6"/>
+      <c r="T33" s="9" t="e">
+        <f t="shared" ref="T33:W33" si="27">+T31/T34</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q33" s="9">
-        <f t="shared" si="26"/>
+      <c r="U33" s="9">
+        <f t="shared" si="27"/>
         <v>-0.54226323305448931</v>
       </c>
-      <c r="R33" s="9">
-        <f t="shared" si="26"/>
+      <c r="V33" s="9">
+        <f t="shared" si="27"/>
         <v>0.14570037888405196</v>
       </c>
-      <c r="S33" s="9">
-        <f t="shared" si="26"/>
+      <c r="W33" s="9">
+        <f t="shared" si="27"/>
         <v>0.76924913584650645</v>
       </c>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6"/>
       <c r="X33" s="6"/>
       <c r="Y33" s="6"/>
       <c r="Z33" s="6"/>
-      <c r="AA33" s="7"/>
-      <c r="AB33" s="7"/>
-      <c r="AC33" s="7"/>
-      <c r="AD33" s="7"/>
+      <c r="AA33" s="6"/>
+      <c r="AB33" s="6"/>
+      <c r="AC33" s="6"/>
+      <c r="AD33" s="6"/>
       <c r="AE33" s="7"/>
       <c r="AF33" s="7"/>
       <c r="AG33" s="7"/>
@@ -3065,8 +3290,12 @@
       <c r="AL33" s="7"/>
       <c r="AM33" s="7"/>
       <c r="AN33" s="7"/>
-    </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO33" s="7"/>
+      <c r="AP33" s="7"/>
+      <c r="AQ33" s="7"/>
+      <c r="AR33" s="7"/>
+    </row>
+    <row r="34" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>3</v>
       </c>
@@ -3106,28 +3335,30 @@
       <c r="N34" s="6">
         <v>556.80298600000003</v>
       </c>
-      <c r="O34" s="6"/>
+      <c r="O34" s="6">
+        <v>564.90232900000001</v>
+      </c>
       <c r="P34" s="6"/>
-      <c r="Q34" s="6">
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
+      <c r="U34" s="6">
         <v>384.49960700000003</v>
       </c>
-      <c r="R34" s="6">
+      <c r="V34" s="6">
         <v>498.28284975000003</v>
       </c>
-      <c r="S34" s="6">
+      <c r="W34" s="6">
         <v>555.60673399999996</v>
       </c>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
       <c r="X34" s="6"/>
       <c r="Y34" s="6"/>
       <c r="Z34" s="6"/>
-      <c r="AA34" s="7"/>
-      <c r="AB34" s="7"/>
-      <c r="AC34" s="7"/>
-      <c r="AD34" s="7"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="6"/>
+      <c r="AD34" s="6"/>
       <c r="AE34" s="7"/>
       <c r="AF34" s="7"/>
       <c r="AG34" s="7"/>
@@ -3138,8 +3369,12 @@
       <c r="AL34" s="7"/>
       <c r="AM34" s="7"/>
       <c r="AN34" s="7"/>
-    </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO34" s="7"/>
+      <c r="AP34" s="7"/>
+      <c r="AQ34" s="7"/>
+      <c r="AR34" s="7"/>
+    </row>
+    <row r="35" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -3178,8 +3413,12 @@
       <c r="AL35" s="7"/>
       <c r="AM35" s="7"/>
       <c r="AN35" s="7"/>
-    </row>
-    <row r="36" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO35" s="7"/>
+      <c r="AP35" s="7"/>
+      <c r="AQ35" s="7"/>
+      <c r="AR35" s="7"/>
+    </row>
+    <row r="36" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>44</v>
       </c>
@@ -3188,55 +3427,58 @@
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="10">
-        <f t="shared" ref="G36:H39" si="27">+G8/C8-1</f>
+        <f t="shared" ref="G36:H39" si="28">+G8/C8-1</f>
         <v>1.0084033613445342E-2</v>
       </c>
       <c r="H36" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8.6956521739129933E-3</v>
       </c>
       <c r="I36" s="10">
-        <f>+I8/E8-1</f>
+        <f t="shared" ref="I36:O36" si="29">+I8/E8-1</f>
         <v>3.874092009685226E-2</v>
       </c>
       <c r="J36" s="10">
-        <f>+J8/F8-1</f>
+        <f t="shared" si="29"/>
         <v>0.15062020082693439</v>
       </c>
       <c r="K36" s="10">
-        <f>+K8/G8-1</f>
+        <f t="shared" si="29"/>
         <v>0.12285080421519678</v>
       </c>
       <c r="L36" s="10">
-        <f>+L8/H8-1</f>
+        <f t="shared" si="29"/>
         <v>0.19051724137931036</v>
       </c>
       <c r="M36" s="10">
-        <f>+M8/I8-1</f>
+        <f t="shared" si="29"/>
         <v>0.23193473193473202</v>
       </c>
       <c r="N36" s="10">
-        <f>+N8/J8-1</f>
+        <f t="shared" si="29"/>
         <v>2.0191649555099334E-2</v>
       </c>
-      <c r="O36" s="7"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="14" t="e">
-        <f t="shared" ref="Q36:S36" si="28">+Q8/P8-1</f>
+      <c r="O36" s="10">
+        <f t="shared" si="29"/>
+        <v>0.59175104964188696</v>
+      </c>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+      <c r="U36" s="13" t="e">
+        <f t="shared" ref="U36:V36" si="30">+U8/T8-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R36" s="14">
-        <f t="shared" si="28"/>
+      <c r="V36" s="13">
+        <f t="shared" si="30"/>
         <v>6.5057364546720509E-2</v>
       </c>
-      <c r="S36" s="14">
-        <f>+S8/R8-1</f>
+      <c r="W36" s="13">
+        <f>+W8/V8-1</f>
         <v>0.12440846824408469</v>
       </c>
-      <c r="T36" s="7"/>
-      <c r="U36" s="7"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="7"/>
       <c r="X36" s="7"/>
       <c r="Y36" s="7"/>
       <c r="Z36" s="7"/>
@@ -3254,8 +3496,12 @@
       <c r="AL36" s="7"/>
       <c r="AM36" s="7"/>
       <c r="AN36" s="7"/>
-    </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO36" s="7"/>
+      <c r="AP36" s="7"/>
+      <c r="AQ36" s="7"/>
+      <c r="AR36" s="7"/>
+    </row>
+    <row r="37" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>45</v>
       </c>
@@ -3264,55 +3510,58 @@
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1.1951219512195133E-2</v>
       </c>
       <c r="H37" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>5.464480874316946E-3</v>
       </c>
       <c r="I37" s="10">
-        <f t="shared" ref="I37:N39" si="29">+I9/E9-1</f>
+        <f t="shared" ref="I37:O39" si="31">+I9/E9-1</f>
         <v>7.2527472527472492E-2</v>
       </c>
       <c r="J37" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>8.0510338759348876E-2</v>
       </c>
       <c r="K37" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.12002892263195952</v>
       </c>
       <c r="L37" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>7.4456521739130421E-2</v>
       </c>
       <c r="M37" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.17663934426229511</v>
       </c>
       <c r="N37" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.40736970684039076</v>
       </c>
-      <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="14" t="e">
-        <f t="shared" ref="Q37:S37" si="30">+Q9/P9-1</f>
+      <c r="O37" s="10">
+        <f t="shared" si="31"/>
+        <v>0.18097697439208082</v>
+      </c>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="13" t="e">
+        <f t="shared" ref="U37:V37" si="32">+U9/T9-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R37" s="14">
-        <f t="shared" si="30"/>
+      <c r="V37" s="13">
+        <f t="shared" si="32"/>
         <v>4.5384432842904721E-2</v>
       </c>
-      <c r="S37" s="14">
-        <f>+S9/R9-1</f>
+      <c r="W37" s="13">
+        <f>+W9/V9-1</f>
         <v>0.20628795187560289</v>
       </c>
-      <c r="T37" s="7"/>
-      <c r="U37" s="7"/>
-      <c r="V37" s="7"/>
-      <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="7"/>
@@ -3330,8 +3579,12 @@
       <c r="AL37" s="7"/>
       <c r="AM37" s="7"/>
       <c r="AN37" s="7"/>
-    </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO37" s="7"/>
+      <c r="AP37" s="7"/>
+      <c r="AQ37" s="7"/>
+      <c r="AR37" s="7"/>
+    </row>
+    <row r="38" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>46</v>
       </c>
@@ -3340,55 +3593,58 @@
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.52</v>
       </c>
       <c r="H38" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.5372340425531914</v>
       </c>
       <c r="I38" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.56499999999999995</v>
       </c>
       <c r="J38" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.5386773547094188</v>
       </c>
       <c r="K38" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.43132220795892162</v>
       </c>
       <c r="L38" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.41937716262975777</v>
       </c>
       <c r="M38" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.47444089456868999</v>
       </c>
       <c r="N38" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.4175566553790051</v>
       </c>
-      <c r="O38" s="7"/>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="14" t="e">
-        <f t="shared" ref="Q38:S38" si="31">+Q10/P10-1</f>
+      <c r="O38" s="10">
+        <f t="shared" si="31"/>
+        <v>0.14977578475336317</v>
+      </c>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="13" t="e">
+        <f t="shared" ref="U38:V38" si="33">+U10/T10-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R38" s="14">
-        <f t="shared" si="31"/>
+      <c r="V38" s="13">
+        <f t="shared" si="33"/>
         <v>0.5400593471810089</v>
       </c>
-      <c r="S38" s="14">
-        <f>+S10/R10-1</f>
+      <c r="W38" s="13">
+        <f>+W10/V10-1</f>
         <v>0.43499036608863206</v>
       </c>
-      <c r="T38" s="7"/>
-      <c r="U38" s="7"/>
-      <c r="V38" s="7"/>
-      <c r="W38" s="7"/>
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
       <c r="Z38" s="7"/>
@@ -3406,8 +3662,12 @@
       <c r="AL38" s="7"/>
       <c r="AM38" s="7"/>
       <c r="AN38" s="7"/>
-    </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO38" s="7"/>
+      <c r="AP38" s="7"/>
+      <c r="AQ38" s="7"/>
+      <c r="AR38" s="7"/>
+    </row>
+    <row r="39" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>47</v>
       </c>
@@ -3416,55 +3676,58 @@
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.35128205128205137</v>
       </c>
       <c r="H39" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.45205479452054798</v>
       </c>
       <c r="I39" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.47058823529411775</v>
       </c>
       <c r="J39" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.52380952380952372</v>
       </c>
       <c r="K39" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.4886148007590132</v>
       </c>
       <c r="L39" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.45754716981132071</v>
       </c>
       <c r="M39" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.53679999999999994</v>
       </c>
       <c r="N39" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.53068181818181803</v>
       </c>
-      <c r="O39" s="7"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="14" t="e">
-        <f t="shared" ref="Q39:S39" si="32">+Q11/P11-1</f>
+      <c r="O39" s="10">
+        <f t="shared" si="31"/>
+        <v>0.52581261950286806</v>
+      </c>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="13" t="e">
+        <f t="shared" ref="U39:V39" si="34">+U11/T11-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R39" s="14">
-        <f t="shared" si="32"/>
+      <c r="V39" s="13">
+        <f t="shared" si="34"/>
         <v>0.45775248933143664</v>
       </c>
-      <c r="S39" s="14">
-        <f>+S11/R11-1</f>
+      <c r="W39" s="13">
+        <f>+W11/V11-1</f>
         <v>0.50839188134270108</v>
       </c>
-      <c r="T39" s="7"/>
-      <c r="U39" s="7"/>
-      <c r="V39" s="7"/>
-      <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="7"/>
@@ -3482,8 +3745,12 @@
       <c r="AL39" s="7"/>
       <c r="AM39" s="7"/>
       <c r="AN39" s="7"/>
-    </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO39" s="7"/>
+      <c r="AP39" s="7"/>
+      <c r="AQ39" s="7"/>
+      <c r="AR39" s="7"/>
+    </row>
+    <row r="40" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>48</v>
       </c>
@@ -3492,55 +3759,58 @@
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="10">
-        <f t="shared" ref="G40:H43" si="33">+G14/C14-1</f>
+        <f t="shared" ref="G40:H43" si="35">+G14/C14-1</f>
         <v>0.45661971830985926</v>
       </c>
       <c r="H40" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.34323432343234317</v>
       </c>
       <c r="I40" s="10">
-        <f>+I14/E14-1</f>
+        <f t="shared" ref="I40:O40" si="36">+I14/E14-1</f>
         <v>0.33676092544987157</v>
       </c>
       <c r="J40" s="10">
-        <f>+J14/F14-1</f>
+        <f t="shared" si="36"/>
         <v>0.33178405434394009</v>
       </c>
       <c r="K40" s="10">
-        <f>+K14/G14-1</f>
+        <f t="shared" si="36"/>
         <v>0.28369754399535863</v>
       </c>
       <c r="L40" s="10">
-        <f>+L14/H14-1</f>
+        <f t="shared" si="36"/>
         <v>0.25036855036855021</v>
       </c>
       <c r="M40" s="10">
-        <f>+M14/I14-1</f>
+        <f t="shared" si="36"/>
         <v>0.31403846153846149</v>
       </c>
       <c r="N40" s="10">
-        <f>+N14/J14-1</f>
+        <f t="shared" si="36"/>
         <v>0.34201342281879188</v>
       </c>
-      <c r="O40" s="7"/>
-      <c r="P40" s="7"/>
-      <c r="Q40" s="14" t="e">
-        <f t="shared" ref="Q40:S40" si="34">+Q14/P14-1</f>
+      <c r="O40" s="10">
+        <f t="shared" si="36"/>
+        <v>0.33323290147634843</v>
+      </c>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="13" t="e">
+        <f t="shared" ref="U40:V40" si="37">+U14/T14-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R40" s="14">
-        <f t="shared" si="34"/>
+      <c r="V40" s="13">
+        <f t="shared" si="37"/>
         <v>0.36273655378486036</v>
       </c>
-      <c r="S40" s="14">
-        <f>+S14/R14-1</f>
+      <c r="W40" s="13">
+        <f>+W14/V14-1</f>
         <v>0.30455438307980454</v>
       </c>
-      <c r="T40" s="7"/>
-      <c r="U40" s="7"/>
-      <c r="V40" s="7"/>
-      <c r="W40" s="7"/>
       <c r="X40" s="7"/>
       <c r="Y40" s="7"/>
       <c r="Z40" s="7"/>
@@ -3558,8 +3828,12 @@
       <c r="AL40" s="7"/>
       <c r="AM40" s="7"/>
       <c r="AN40" s="7"/>
-    </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO40" s="7"/>
+      <c r="AP40" s="7"/>
+      <c r="AQ40" s="7"/>
+      <c r="AR40" s="7"/>
+    </row>
+    <row r="41" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>49</v>
       </c>
@@ -3568,55 +3842,58 @@
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>6.5782493368700345E-2</v>
       </c>
       <c r="H41" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.10948905109489049</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" ref="I41:N43" si="35">+I15/E15-1</f>
+        <f t="shared" ref="I41:O43" si="38">+I15/E15-1</f>
         <v>7.8787878787878851E-2</v>
       </c>
       <c r="J41" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.13070776255707739</v>
       </c>
       <c r="K41" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.25037332005973112</v>
       </c>
       <c r="L41" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.36085526315789473</v>
       </c>
       <c r="M41" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.35486891385767794</v>
       </c>
       <c r="N41" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.28571428571428581</v>
       </c>
-      <c r="O41" s="7"/>
-      <c r="P41" s="7"/>
-      <c r="Q41" s="14" t="e">
-        <f t="shared" ref="Q41:S41" si="36">+Q15/P15-1</f>
+      <c r="O41" s="10">
+        <f t="shared" si="38"/>
+        <v>0.42038216560509567</v>
+      </c>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="13" t="e">
+        <f t="shared" ref="U41:V41" si="39">+U15/T15-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R41" s="14">
-        <f t="shared" si="36"/>
+      <c r="V41" s="13">
+        <f t="shared" si="39"/>
         <v>9.7212251734864807E-2</v>
       </c>
-      <c r="S41" s="14">
-        <f>+S15/R15-1</f>
+      <c r="W41" s="13">
+        <f>+W15/V15-1</f>
         <v>0.31056103811133529</v>
       </c>
-      <c r="T41" s="7"/>
-      <c r="U41" s="7"/>
-      <c r="V41" s="7"/>
-      <c r="W41" s="7"/>
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="7"/>
@@ -3634,8 +3911,12 @@
       <c r="AL41" s="7"/>
       <c r="AM41" s="7"/>
       <c r="AN41" s="7"/>
-    </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO41" s="7"/>
+      <c r="AP41" s="7"/>
+      <c r="AQ41" s="7"/>
+      <c r="AR41" s="7"/>
+    </row>
+    <row r="42" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>50</v>
       </c>
@@ -3644,55 +3925,58 @@
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-0.13962264150943393</v>
       </c>
       <c r="H42" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1.0714285714285676E-2</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>-0.2592592592592593</v>
       </c>
       <c r="J42" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.22144329896907222</v>
       </c>
       <c r="K42" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.11951754385964897</v>
       </c>
       <c r="L42" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.1084805653710248</v>
       </c>
       <c r="M42" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.74750000000000005</v>
       </c>
       <c r="N42" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.13841998649561105</v>
       </c>
-      <c r="O42" s="7"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="14" t="e">
-        <f t="shared" ref="Q42:S42" si="37">+Q16/P16-1</f>
+      <c r="O42" s="10">
+        <f t="shared" si="38"/>
+        <v>0.13254978778974857</v>
+      </c>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+      <c r="U42" s="13" t="e">
+        <f t="shared" ref="U42:V42" si="40">+U16/T16-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R42" s="14">
-        <f t="shared" si="37"/>
+      <c r="V42" s="13">
+        <f t="shared" si="40"/>
         <v>-5.1958577217469659E-2</v>
       </c>
-      <c r="S42" s="14">
-        <f>+S16/R16-1</f>
+      <c r="W42" s="13">
+        <f>+W16/V16-1</f>
         <v>0.24116641337386024</v>
       </c>
-      <c r="T42" s="7"/>
-      <c r="U42" s="7"/>
-      <c r="V42" s="7"/>
-      <c r="W42" s="7"/>
       <c r="X42" s="7"/>
       <c r="Y42" s="7"/>
       <c r="Z42" s="7"/>
@@ -3710,8 +3994,12 @@
       <c r="AL42" s="7"/>
       <c r="AM42" s="7"/>
       <c r="AN42" s="7"/>
-    </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO42" s="7"/>
+      <c r="AP42" s="7"/>
+      <c r="AQ42" s="7"/>
+      <c r="AR42" s="7"/>
+    </row>
+    <row r="43" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B43" s="4" t="s">
         <v>51</v>
       </c>
@@ -3720,55 +4008,58 @@
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.13538988860325629</v>
       </c>
       <c r="H43" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.15989729225023352</v>
       </c>
       <c r="I43" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.17405255398491026</v>
       </c>
       <c r="J43" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.23201506591337107</v>
       </c>
       <c r="K43" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.23480083857442358</v>
       </c>
       <c r="L43" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.24401287985510156</v>
       </c>
       <c r="M43" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.29731127197518092</v>
       </c>
       <c r="N43" s="12">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.28468358300213992</v>
       </c>
-      <c r="O43" s="7"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="12" t="e">
-        <f t="shared" ref="Q43:S43" si="38">+Q17/P17-1</f>
+      <c r="O43" s="12">
+        <f t="shared" si="38"/>
+        <v>0.32122241086587433</v>
+      </c>
+      <c r="P43" s="12"/>
+      <c r="Q43" s="12"/>
+      <c r="R43" s="12"/>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="U43" s="12" t="e">
+        <f t="shared" ref="U43:V43" si="41">+U17/T17-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R43" s="12">
-        <f t="shared" si="38"/>
+      <c r="V43" s="12">
+        <f t="shared" si="41"/>
         <v>0.17957016204389564</v>
       </c>
-      <c r="S43" s="12">
-        <f>+S17/R17-1</f>
+      <c r="W43" s="12">
+        <f>+W17/V17-1</f>
         <v>0.26868382409768898</v>
       </c>
-      <c r="T43" s="7"/>
-      <c r="U43" s="7"/>
-      <c r="V43" s="7"/>
-      <c r="W43" s="7"/>
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="7"/>
@@ -3786,80 +4077,87 @@
       <c r="AL43" s="7"/>
       <c r="AM43" s="7"/>
       <c r="AN43" s="7"/>
-    </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO43" s="7"/>
+      <c r="AP43" s="7"/>
+      <c r="AQ43" s="7"/>
+      <c r="AR43" s="7"/>
+    </row>
+    <row r="44" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C44" s="10">
-        <f t="shared" ref="C44:H44" si="39">+C19/C17</f>
+        <f t="shared" ref="C44:H44" si="42">+C19/C17</f>
         <v>0.52832524040750262</v>
       </c>
       <c r="D44" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.53291316526610644</v>
       </c>
       <c r="E44" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.51010320006937815</v>
       </c>
       <c r="F44" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.52406779661016956</v>
       </c>
       <c r="G44" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.5434800838574424</v>
       </c>
       <c r="H44" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.55473938418192792</v>
       </c>
       <c r="I44" s="10">
-        <f>+I19/I17</f>
+        <f t="shared" ref="I44:N44" si="43">+I19/I17</f>
         <v>0.55200177278770868</v>
       </c>
       <c r="J44" s="10">
-        <f>+J19/J17</f>
+        <f t="shared" si="43"/>
         <v>0.56099052277590955</v>
       </c>
       <c r="K44" s="10">
-        <f>+K19/K17</f>
+        <f t="shared" si="43"/>
         <v>0.57799660441426148</v>
       </c>
       <c r="L44" s="10">
-        <f>+L19/L17</f>
+        <f t="shared" si="43"/>
         <v>0.58472862573808948</v>
       </c>
       <c r="M44" s="10">
-        <f>+M19/M17</f>
+        <f t="shared" si="43"/>
         <v>0.56835392586687916</v>
       </c>
       <c r="N44" s="10">
-        <f>+N19/N17</f>
+        <f t="shared" si="43"/>
         <v>0.5768882966065394</v>
       </c>
-      <c r="O44" s="7"/>
-      <c r="P44" s="10" t="e">
-        <f t="shared" ref="P44:S44" si="40">+P19/P17</f>
+      <c r="O44" s="10">
+        <f t="shared" ref="O44" si="44">+O19/O17</f>
+        <v>0.59902338730403504</v>
+      </c>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="7"/>
+      <c r="T44" s="10" t="e">
+        <f t="shared" ref="T44:W44" si="45">+T19/T17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q44" s="10">
-        <f t="shared" ref="Q44:S44" si="41">+Q19/Q17</f>
+      <c r="U44" s="10">
+        <f t="shared" ref="U44:V44" si="46">+U19/U17</f>
         <v>0.52314424413701932</v>
       </c>
-      <c r="R44" s="10">
-        <f t="shared" si="41"/>
+      <c r="V44" s="10">
+        <f t="shared" si="46"/>
         <v>0.55340443620063373</v>
       </c>
-      <c r="S44" s="10">
-        <f t="shared" si="40"/>
+      <c r="W44" s="10">
+        <f t="shared" si="45"/>
         <v>0.57633029758459986</v>
       </c>
-      <c r="T44" s="7"/>
-      <c r="U44" s="7"/>
-      <c r="V44" s="7"/>
-      <c r="W44" s="7"/>
       <c r="X44" s="7"/>
       <c r="Y44" s="7"/>
       <c r="Z44" s="7"/>
@@ -3877,80 +4175,87 @@
       <c r="AL44" s="7"/>
       <c r="AM44" s="7"/>
       <c r="AN44" s="7"/>
-    </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO44" s="7"/>
+      <c r="AP44" s="7"/>
+      <c r="AQ44" s="7"/>
+      <c r="AR44" s="7"/>
+    </row>
+    <row r="45" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C45" s="10">
-        <f t="shared" ref="C45:H45" si="42">+C23/C17</f>
+        <f t="shared" ref="C45:H45" si="47">+C23/C17</f>
         <v>0.12415500333238121</v>
       </c>
       <c r="D45" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>8.7535014005601722E-3</v>
       </c>
       <c r="E45" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>9.0798716503338761E-2</v>
       </c>
       <c r="F45" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>4.5047080979284407E-2</v>
       </c>
       <c r="G45" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>9.1404612159329199E-2</v>
       </c>
       <c r="H45" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>-8.5530287784263345E-3</v>
       </c>
       <c r="I45" s="10">
-        <f>+I23/I17</f>
+        <f t="shared" ref="I45:N45" si="48">+I23/I17</f>
         <v>0.13052149505096763</v>
       </c>
       <c r="J45" s="10">
-        <f>+J23/J17</f>
+        <f t="shared" si="48"/>
         <v>0.11837358605930912</v>
       </c>
       <c r="K45" s="10">
-        <f>+K23/K17</f>
+        <f t="shared" si="48"/>
         <v>0.14546689303904928</v>
       </c>
       <c r="L45" s="10">
-        <f>+L23/L17</f>
+        <f t="shared" si="48"/>
         <v>3.5347407587155238E-2</v>
       </c>
       <c r="M45" s="10">
-        <f>+M23/M17</f>
+        <f t="shared" si="48"/>
         <v>0.12292888458691563</v>
       </c>
       <c r="N45" s="10">
-        <f>+N23/N17</f>
+        <f t="shared" si="48"/>
         <v>0.10851458759697299</v>
       </c>
-      <c r="O45" s="7"/>
-      <c r="P45" s="10" t="e">
-        <f t="shared" ref="P45:S45" si="43">+P23/P17</f>
+      <c r="O45" s="10">
+        <f t="shared" ref="O45" si="49">+O23/O17</f>
+        <v>0.16504754561809307</v>
+      </c>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="7"/>
+      <c r="T45" s="10" t="e">
+        <f t="shared" ref="T45:W45" si="50">+T23/T17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q45" s="10">
-        <f t="shared" ref="Q45:S45" si="44">+Q23/Q17</f>
+      <c r="U45" s="10">
+        <f t="shared" ref="U45:V45" si="51">+U23/U17</f>
         <v>6.891993527360564E-2</v>
       </c>
-      <c r="R45" s="10">
-        <f t="shared" si="44"/>
+      <c r="V45" s="10">
+        <f t="shared" si="51"/>
         <v>9.0965298709328402E-2</v>
       </c>
-      <c r="S45" s="10">
-        <f t="shared" si="43"/>
+      <c r="W45" s="10">
+        <f t="shared" si="50"/>
         <v>0.10688069202887512</v>
       </c>
-      <c r="T45" s="7"/>
-      <c r="U45" s="7"/>
-      <c r="V45" s="7"/>
-      <c r="W45" s="7"/>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="7"/>
@@ -3968,80 +4273,87 @@
       <c r="AL45" s="7"/>
       <c r="AM45" s="7"/>
       <c r="AN45" s="7"/>
-    </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO45" s="7"/>
+      <c r="AP45" s="7"/>
+      <c r="AQ45" s="7"/>
+      <c r="AR45" s="7"/>
+    </row>
+    <row r="46" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C46" s="10">
-        <f t="shared" ref="C46:H46" si="45">+C28/C27</f>
+        <f t="shared" ref="C46:H46" si="52">+C28/C27</f>
         <v>0.58333333333333348</v>
       </c>
       <c r="D46" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>-5.6644880174291916E-2</v>
       </c>
       <c r="E46" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>-9.878787878787632</v>
       </c>
       <c r="F46" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>-0.72363636363636419</v>
       </c>
       <c r="G46" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0.54304635761589126</v>
       </c>
       <c r="H46" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0.96648044692737256</v>
       </c>
       <c r="I46" s="10">
-        <f>+I28/I27</f>
+        <f t="shared" ref="I46:N46" si="53">+I28/I27</f>
         <v>0.56400310318076052</v>
       </c>
       <c r="J46" s="10">
-        <f>+J28/J27</f>
+        <f t="shared" si="53"/>
         <v>0.75881523272214313</v>
       </c>
       <c r="K46" s="10">
-        <f>+K28/K27</f>
+        <f t="shared" si="53"/>
         <v>0.30111336032388658</v>
       </c>
       <c r="L46" s="10">
-        <f>+L28/L27</f>
+        <f t="shared" si="53"/>
         <v>-2.7522935779816491E-2</v>
       </c>
       <c r="M46" s="10">
-        <f>+M28/M27</f>
+        <f t="shared" si="53"/>
         <v>0.25948406676783015</v>
       </c>
       <c r="N46" s="10">
-        <f>+N28/N27</f>
+        <f t="shared" si="53"/>
         <v>0.35631629701060763</v>
       </c>
-      <c r="O46" s="7"/>
-      <c r="P46" s="10" t="e">
-        <f t="shared" ref="P46:S46" si="46">+P28/P27</f>
+      <c r="O46" s="10">
+        <f t="shared" ref="O46" si="54">+O28/O27</f>
+        <v>0.29301745635910215</v>
+      </c>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="10" t="e">
+        <f t="shared" ref="T46:W46" si="55">+T28/T27</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q46" s="10">
-        <f t="shared" ref="Q46:S46" si="47">+Q28/Q27</f>
+      <c r="U46" s="10">
+        <f t="shared" ref="U46:V46" si="56">+U28/U27</f>
         <v>-0.99712918660286554</v>
       </c>
-      <c r="R46" s="10">
-        <f t="shared" si="47"/>
+      <c r="V46" s="10">
+        <f t="shared" si="56"/>
         <v>0.51364764267990026</v>
       </c>
-      <c r="S46" s="10">
-        <f t="shared" si="46"/>
+      <c r="W46" s="10">
+        <f t="shared" si="55"/>
         <v>0.29479583666933556</v>
       </c>
-      <c r="T46" s="7"/>
-      <c r="U46" s="7"/>
-      <c r="V46" s="7"/>
-      <c r="W46" s="7"/>
       <c r="X46" s="7"/>
       <c r="Y46" s="7"/>
       <c r="Z46" s="7"/>
@@ -4059,8 +4371,12 @@
       <c r="AL46" s="7"/>
       <c r="AM46" s="7"/>
       <c r="AN46" s="7"/>
-    </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO46" s="7"/>
+      <c r="AP46" s="7"/>
+      <c r="AQ46" s="7"/>
+      <c r="AR46" s="7"/>
+    </row>
+    <row r="47" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
@@ -4099,8 +4415,12 @@
       <c r="AL47" s="7"/>
       <c r="AM47" s="7"/>
       <c r="AN47" s="7"/>
-    </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="AO47" s="7"/>
+      <c r="AP47" s="7"/>
+      <c r="AQ47" s="7"/>
+      <c r="AR47" s="7"/>
+    </row>
+    <row r="48" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
@@ -4139,8 +4459,12 @@
       <c r="AL48" s="7"/>
       <c r="AM48" s="7"/>
       <c r="AN48" s="7"/>
-    </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO48" s="7"/>
+      <c r="AP48" s="7"/>
+      <c r="AQ48" s="7"/>
+      <c r="AR48" s="7"/>
+    </row>
+    <row r="49" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
@@ -4179,8 +4503,12 @@
       <c r="AL49" s="7"/>
       <c r="AM49" s="7"/>
       <c r="AN49" s="7"/>
-    </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO49" s="7"/>
+      <c r="AP49" s="7"/>
+      <c r="AQ49" s="7"/>
+      <c r="AR49" s="7"/>
+    </row>
+    <row r="50" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
@@ -4219,8 +4547,12 @@
       <c r="AL50" s="7"/>
       <c r="AM50" s="7"/>
       <c r="AN50" s="7"/>
-    </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO50" s="7"/>
+      <c r="AP50" s="7"/>
+      <c r="AQ50" s="7"/>
+      <c r="AR50" s="7"/>
+    </row>
+    <row r="51" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
@@ -4259,8 +4591,12 @@
       <c r="AL51" s="7"/>
       <c r="AM51" s="7"/>
       <c r="AN51" s="7"/>
-    </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO51" s="7"/>
+      <c r="AP51" s="7"/>
+      <c r="AQ51" s="7"/>
+      <c r="AR51" s="7"/>
+    </row>
+    <row r="52" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
@@ -4299,8 +4635,12 @@
       <c r="AL52" s="7"/>
       <c r="AM52" s="7"/>
       <c r="AN52" s="7"/>
-    </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO52" s="7"/>
+      <c r="AP52" s="7"/>
+      <c r="AQ52" s="7"/>
+      <c r="AR52" s="7"/>
+    </row>
+    <row r="53" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
@@ -4339,8 +4679,12 @@
       <c r="AL53" s="7"/>
       <c r="AM53" s="7"/>
       <c r="AN53" s="7"/>
-    </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO53" s="7"/>
+      <c r="AP53" s="7"/>
+      <c r="AQ53" s="7"/>
+      <c r="AR53" s="7"/>
+    </row>
+    <row r="54" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
@@ -4379,8 +4723,12 @@
       <c r="AL54" s="7"/>
       <c r="AM54" s="7"/>
       <c r="AN54" s="7"/>
-    </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO54" s="7"/>
+      <c r="AP54" s="7"/>
+      <c r="AQ54" s="7"/>
+      <c r="AR54" s="7"/>
+    </row>
+    <row r="55" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
@@ -4419,8 +4767,12 @@
       <c r="AL55" s="7"/>
       <c r="AM55" s="7"/>
       <c r="AN55" s="7"/>
-    </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO55" s="7"/>
+      <c r="AP55" s="7"/>
+      <c r="AQ55" s="7"/>
+      <c r="AR55" s="7"/>
+    </row>
+    <row r="56" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
@@ -4459,8 +4811,12 @@
       <c r="AL56" s="7"/>
       <c r="AM56" s="7"/>
       <c r="AN56" s="7"/>
-    </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO56" s="7"/>
+      <c r="AP56" s="7"/>
+      <c r="AQ56" s="7"/>
+      <c r="AR56" s="7"/>
+    </row>
+    <row r="57" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
@@ -4499,8 +4855,12 @@
       <c r="AL57" s="7"/>
       <c r="AM57" s="7"/>
       <c r="AN57" s="7"/>
-    </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO57" s="7"/>
+      <c r="AP57" s="7"/>
+      <c r="AQ57" s="7"/>
+      <c r="AR57" s="7"/>
+    </row>
+    <row r="58" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
@@ -4539,8 +4899,12 @@
       <c r="AL58" s="7"/>
       <c r="AM58" s="7"/>
       <c r="AN58" s="7"/>
-    </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO58" s="7"/>
+      <c r="AP58" s="7"/>
+      <c r="AQ58" s="7"/>
+      <c r="AR58" s="7"/>
+    </row>
+    <row r="59" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
@@ -4579,8 +4943,12 @@
       <c r="AL59" s="7"/>
       <c r="AM59" s="7"/>
       <c r="AN59" s="7"/>
-    </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO59" s="7"/>
+      <c r="AP59" s="7"/>
+      <c r="AQ59" s="7"/>
+      <c r="AR59" s="7"/>
+    </row>
+    <row r="60" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
@@ -4619,8 +4987,12 @@
       <c r="AL60" s="7"/>
       <c r="AM60" s="7"/>
       <c r="AN60" s="7"/>
-    </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO60" s="7"/>
+      <c r="AP60" s="7"/>
+      <c r="AQ60" s="7"/>
+      <c r="AR60" s="7"/>
+    </row>
+    <row r="61" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
@@ -4659,8 +5031,12 @@
       <c r="AL61" s="7"/>
       <c r="AM61" s="7"/>
       <c r="AN61" s="7"/>
-    </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO61" s="7"/>
+      <c r="AP61" s="7"/>
+      <c r="AQ61" s="7"/>
+      <c r="AR61" s="7"/>
+    </row>
+    <row r="62" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
@@ -4699,8 +5075,12 @@
       <c r="AL62" s="7"/>
       <c r="AM62" s="7"/>
       <c r="AN62" s="7"/>
-    </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO62" s="7"/>
+      <c r="AP62" s="7"/>
+      <c r="AQ62" s="7"/>
+      <c r="AR62" s="7"/>
+    </row>
+    <row r="63" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
@@ -4739,8 +5119,12 @@
       <c r="AL63" s="7"/>
       <c r="AM63" s="7"/>
       <c r="AN63" s="7"/>
-    </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO63" s="7"/>
+      <c r="AP63" s="7"/>
+      <c r="AQ63" s="7"/>
+      <c r="AR63" s="7"/>
+    </row>
+    <row r="64" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
@@ -4779,8 +5163,12 @@
       <c r="AL64" s="7"/>
       <c r="AM64" s="7"/>
       <c r="AN64" s="7"/>
-    </row>
-    <row r="65" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO64" s="7"/>
+      <c r="AP64" s="7"/>
+      <c r="AQ64" s="7"/>
+      <c r="AR64" s="7"/>
+    </row>
+    <row r="65" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
@@ -4819,8 +5207,12 @@
       <c r="AL65" s="7"/>
       <c r="AM65" s="7"/>
       <c r="AN65" s="7"/>
-    </row>
-    <row r="66" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO65" s="7"/>
+      <c r="AP65" s="7"/>
+      <c r="AQ65" s="7"/>
+      <c r="AR65" s="7"/>
+    </row>
+    <row r="66" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
@@ -4859,8 +5251,12 @@
       <c r="AL66" s="7"/>
       <c r="AM66" s="7"/>
       <c r="AN66" s="7"/>
-    </row>
-    <row r="67" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO66" s="7"/>
+      <c r="AP66" s="7"/>
+      <c r="AQ66" s="7"/>
+      <c r="AR66" s="7"/>
+    </row>
+    <row r="67" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
@@ -4899,8 +5295,12 @@
       <c r="AL67" s="7"/>
       <c r="AM67" s="7"/>
       <c r="AN67" s="7"/>
-    </row>
-    <row r="68" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO67" s="7"/>
+      <c r="AP67" s="7"/>
+      <c r="AQ67" s="7"/>
+      <c r="AR67" s="7"/>
+    </row>
+    <row r="68" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
       <c r="E68" s="7"/>
@@ -4939,8 +5339,12 @@
       <c r="AL68" s="7"/>
       <c r="AM68" s="7"/>
       <c r="AN68" s="7"/>
-    </row>
-    <row r="69" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO68" s="7"/>
+      <c r="AP68" s="7"/>
+      <c r="AQ68" s="7"/>
+      <c r="AR68" s="7"/>
+    </row>
+    <row r="69" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
@@ -4979,8 +5383,12 @@
       <c r="AL69" s="7"/>
       <c r="AM69" s="7"/>
       <c r="AN69" s="7"/>
-    </row>
-    <row r="70" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO69" s="7"/>
+      <c r="AP69" s="7"/>
+      <c r="AQ69" s="7"/>
+      <c r="AR69" s="7"/>
+    </row>
+    <row r="70" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7"/>
@@ -5019,8 +5427,12 @@
       <c r="AL70" s="7"/>
       <c r="AM70" s="7"/>
       <c r="AN70" s="7"/>
-    </row>
-    <row r="71" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO70" s="7"/>
+      <c r="AP70" s="7"/>
+      <c r="AQ70" s="7"/>
+      <c r="AR70" s="7"/>
+    </row>
+    <row r="71" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
@@ -5059,8 +5471,12 @@
       <c r="AL71" s="7"/>
       <c r="AM71" s="7"/>
       <c r="AN71" s="7"/>
-    </row>
-    <row r="72" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO71" s="7"/>
+      <c r="AP71" s="7"/>
+      <c r="AQ71" s="7"/>
+      <c r="AR71" s="7"/>
+    </row>
+    <row r="72" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7"/>
@@ -5099,8 +5515,12 @@
       <c r="AL72" s="7"/>
       <c r="AM72" s="7"/>
       <c r="AN72" s="7"/>
-    </row>
-    <row r="73" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO72" s="7"/>
+      <c r="AP72" s="7"/>
+      <c r="AQ72" s="7"/>
+      <c r="AR72" s="7"/>
+    </row>
+    <row r="73" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
@@ -5139,8 +5559,12 @@
       <c r="AL73" s="7"/>
       <c r="AM73" s="7"/>
       <c r="AN73" s="7"/>
-    </row>
-    <row r="74" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO73" s="7"/>
+      <c r="AP73" s="7"/>
+      <c r="AQ73" s="7"/>
+      <c r="AR73" s="7"/>
+    </row>
+    <row r="74" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
       <c r="E74" s="7"/>
@@ -5179,8 +5603,12 @@
       <c r="AL74" s="7"/>
       <c r="AM74" s="7"/>
       <c r="AN74" s="7"/>
-    </row>
-    <row r="75" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO74" s="7"/>
+      <c r="AP74" s="7"/>
+      <c r="AQ74" s="7"/>
+      <c r="AR74" s="7"/>
+    </row>
+    <row r="75" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
@@ -5219,8 +5647,12 @@
       <c r="AL75" s="7"/>
       <c r="AM75" s="7"/>
       <c r="AN75" s="7"/>
-    </row>
-    <row r="76" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO75" s="7"/>
+      <c r="AP75" s="7"/>
+      <c r="AQ75" s="7"/>
+      <c r="AR75" s="7"/>
+    </row>
+    <row r="76" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7"/>
@@ -5259,8 +5691,12 @@
       <c r="AL76" s="7"/>
       <c r="AM76" s="7"/>
       <c r="AN76" s="7"/>
-    </row>
-    <row r="77" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO76" s="7"/>
+      <c r="AP76" s="7"/>
+      <c r="AQ76" s="7"/>
+      <c r="AR76" s="7"/>
+    </row>
+    <row r="77" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
@@ -5299,8 +5735,12 @@
       <c r="AL77" s="7"/>
       <c r="AM77" s="7"/>
       <c r="AN77" s="7"/>
-    </row>
-    <row r="78" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO77" s="7"/>
+      <c r="AP77" s="7"/>
+      <c r="AQ77" s="7"/>
+      <c r="AR77" s="7"/>
+    </row>
+    <row r="78" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
@@ -5339,8 +5779,12 @@
       <c r="AL78" s="7"/>
       <c r="AM78" s="7"/>
       <c r="AN78" s="7"/>
-    </row>
-    <row r="79" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO78" s="7"/>
+      <c r="AP78" s="7"/>
+      <c r="AQ78" s="7"/>
+      <c r="AR78" s="7"/>
+    </row>
+    <row r="79" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
       <c r="E79" s="7"/>
@@ -5379,8 +5823,12 @@
       <c r="AL79" s="7"/>
       <c r="AM79" s="7"/>
       <c r="AN79" s="7"/>
-    </row>
-    <row r="80" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO79" s="7"/>
+      <c r="AP79" s="7"/>
+      <c r="AQ79" s="7"/>
+      <c r="AR79" s="7"/>
+    </row>
+    <row r="80" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
       <c r="E80" s="7"/>
@@ -5419,8 +5867,12 @@
       <c r="AL80" s="7"/>
       <c r="AM80" s="7"/>
       <c r="AN80" s="7"/>
-    </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO80" s="7"/>
+      <c r="AP80" s="7"/>
+      <c r="AQ80" s="7"/>
+      <c r="AR80" s="7"/>
+    </row>
+    <row r="81" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
       <c r="E81" s="7"/>
@@ -5459,8 +5911,12 @@
       <c r="AL81" s="7"/>
       <c r="AM81" s="7"/>
       <c r="AN81" s="7"/>
-    </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO81" s="7"/>
+      <c r="AP81" s="7"/>
+      <c r="AQ81" s="7"/>
+      <c r="AR81" s="7"/>
+    </row>
+    <row r="82" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
@@ -5499,8 +5955,12 @@
       <c r="AL82" s="7"/>
       <c r="AM82" s="7"/>
       <c r="AN82" s="7"/>
-    </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO82" s="7"/>
+      <c r="AP82" s="7"/>
+      <c r="AQ82" s="7"/>
+      <c r="AR82" s="7"/>
+    </row>
+    <row r="83" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
@@ -5539,8 +5999,12 @@
       <c r="AL83" s="7"/>
       <c r="AM83" s="7"/>
       <c r="AN83" s="7"/>
-    </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO83" s="7"/>
+      <c r="AP83" s="7"/>
+      <c r="AQ83" s="7"/>
+      <c r="AR83" s="7"/>
+    </row>
+    <row r="84" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
@@ -5579,8 +6043,12 @@
       <c r="AL84" s="7"/>
       <c r="AM84" s="7"/>
       <c r="AN84" s="7"/>
-    </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO84" s="7"/>
+      <c r="AP84" s="7"/>
+      <c r="AQ84" s="7"/>
+      <c r="AR84" s="7"/>
+    </row>
+    <row r="85" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
@@ -5619,8 +6087,12 @@
       <c r="AL85" s="7"/>
       <c r="AM85" s="7"/>
       <c r="AN85" s="7"/>
-    </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO85" s="7"/>
+      <c r="AP85" s="7"/>
+      <c r="AQ85" s="7"/>
+      <c r="AR85" s="7"/>
+    </row>
+    <row r="86" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
@@ -5659,8 +6131,12 @@
       <c r="AL86" s="7"/>
       <c r="AM86" s="7"/>
       <c r="AN86" s="7"/>
-    </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO86" s="7"/>
+      <c r="AP86" s="7"/>
+      <c r="AQ86" s="7"/>
+      <c r="AR86" s="7"/>
+    </row>
+    <row r="87" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
       <c r="E87" s="7"/>
@@ -5699,8 +6175,12 @@
       <c r="AL87" s="7"/>
       <c r="AM87" s="7"/>
       <c r="AN87" s="7"/>
-    </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO87" s="7"/>
+      <c r="AP87" s="7"/>
+      <c r="AQ87" s="7"/>
+      <c r="AR87" s="7"/>
+    </row>
+    <row r="88" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
@@ -5739,8 +6219,12 @@
       <c r="AL88" s="7"/>
       <c r="AM88" s="7"/>
       <c r="AN88" s="7"/>
-    </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO88" s="7"/>
+      <c r="AP88" s="7"/>
+      <c r="AQ88" s="7"/>
+      <c r="AR88" s="7"/>
+    </row>
+    <row r="89" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
@@ -5779,8 +6263,12 @@
       <c r="AL89" s="7"/>
       <c r="AM89" s="7"/>
       <c r="AN89" s="7"/>
-    </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO89" s="7"/>
+      <c r="AP89" s="7"/>
+      <c r="AQ89" s="7"/>
+      <c r="AR89" s="7"/>
+    </row>
+    <row r="90" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
@@ -5819,8 +6307,12 @@
       <c r="AL90" s="7"/>
       <c r="AM90" s="7"/>
       <c r="AN90" s="7"/>
-    </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO90" s="7"/>
+      <c r="AP90" s="7"/>
+      <c r="AQ90" s="7"/>
+      <c r="AR90" s="7"/>
+    </row>
+    <row r="91" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
       <c r="E91" s="7"/>
@@ -5859,8 +6351,12 @@
       <c r="AL91" s="7"/>
       <c r="AM91" s="7"/>
       <c r="AN91" s="7"/>
-    </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO91" s="7"/>
+      <c r="AP91" s="7"/>
+      <c r="AQ91" s="7"/>
+      <c r="AR91" s="7"/>
+    </row>
+    <row r="92" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
@@ -5899,8 +6395,12 @@
       <c r="AL92" s="7"/>
       <c r="AM92" s="7"/>
       <c r="AN92" s="7"/>
-    </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO92" s="7"/>
+      <c r="AP92" s="7"/>
+      <c r="AQ92" s="7"/>
+      <c r="AR92" s="7"/>
+    </row>
+    <row r="93" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
@@ -5939,8 +6439,12 @@
       <c r="AL93" s="7"/>
       <c r="AM93" s="7"/>
       <c r="AN93" s="7"/>
-    </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO93" s="7"/>
+      <c r="AP93" s="7"/>
+      <c r="AQ93" s="7"/>
+      <c r="AR93" s="7"/>
+    </row>
+    <row r="94" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
@@ -5979,8 +6483,12 @@
       <c r="AL94" s="7"/>
       <c r="AM94" s="7"/>
       <c r="AN94" s="7"/>
-    </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO94" s="7"/>
+      <c r="AP94" s="7"/>
+      <c r="AQ94" s="7"/>
+      <c r="AR94" s="7"/>
+    </row>
+    <row r="95" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
@@ -6019,8 +6527,12 @@
       <c r="AL95" s="7"/>
       <c r="AM95" s="7"/>
       <c r="AN95" s="7"/>
-    </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO95" s="7"/>
+      <c r="AP95" s="7"/>
+      <c r="AQ95" s="7"/>
+      <c r="AR95" s="7"/>
+    </row>
+    <row r="96" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
@@ -6059,8 +6571,12 @@
       <c r="AL96" s="7"/>
       <c r="AM96" s="7"/>
       <c r="AN96" s="7"/>
-    </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO96" s="7"/>
+      <c r="AP96" s="7"/>
+      <c r="AQ96" s="7"/>
+      <c r="AR96" s="7"/>
+    </row>
+    <row r="97" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
@@ -6099,8 +6615,12 @@
       <c r="AL97" s="7"/>
       <c r="AM97" s="7"/>
       <c r="AN97" s="7"/>
-    </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO97" s="7"/>
+      <c r="AP97" s="7"/>
+      <c r="AQ97" s="7"/>
+      <c r="AR97" s="7"/>
+    </row>
+    <row r="98" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
@@ -6139,8 +6659,12 @@
       <c r="AL98" s="7"/>
       <c r="AM98" s="7"/>
       <c r="AN98" s="7"/>
-    </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO98" s="7"/>
+      <c r="AP98" s="7"/>
+      <c r="AQ98" s="7"/>
+      <c r="AR98" s="7"/>
+    </row>
+    <row r="99" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
       <c r="E99" s="7"/>
@@ -6179,8 +6703,12 @@
       <c r="AL99" s="7"/>
       <c r="AM99" s="7"/>
       <c r="AN99" s="7"/>
-    </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO99" s="7"/>
+      <c r="AP99" s="7"/>
+      <c r="AQ99" s="7"/>
+      <c r="AR99" s="7"/>
+    </row>
+    <row r="100" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
@@ -6219,8 +6747,12 @@
       <c r="AL100" s="7"/>
       <c r="AM100" s="7"/>
       <c r="AN100" s="7"/>
-    </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO100" s="7"/>
+      <c r="AP100" s="7"/>
+      <c r="AQ100" s="7"/>
+      <c r="AR100" s="7"/>
+    </row>
+    <row r="101" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C101" s="7"/>
       <c r="D101" s="7"/>
       <c r="E101" s="7"/>
@@ -6259,8 +6791,12 @@
       <c r="AL101" s="7"/>
       <c r="AM101" s="7"/>
       <c r="AN101" s="7"/>
-    </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO101" s="7"/>
+      <c r="AP101" s="7"/>
+      <c r="AQ101" s="7"/>
+      <c r="AR101" s="7"/>
+    </row>
+    <row r="102" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
@@ -6299,8 +6835,12 @@
       <c r="AL102" s="7"/>
       <c r="AM102" s="7"/>
       <c r="AN102" s="7"/>
-    </row>
-    <row r="103" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO102" s="7"/>
+      <c r="AP102" s="7"/>
+      <c r="AQ102" s="7"/>
+      <c r="AR102" s="7"/>
+    </row>
+    <row r="103" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C103" s="7"/>
       <c r="D103" s="7"/>
       <c r="E103" s="7"/>
@@ -6339,8 +6879,12 @@
       <c r="AL103" s="7"/>
       <c r="AM103" s="7"/>
       <c r="AN103" s="7"/>
-    </row>
-    <row r="104" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO103" s="7"/>
+      <c r="AP103" s="7"/>
+      <c r="AQ103" s="7"/>
+      <c r="AR103" s="7"/>
+    </row>
+    <row r="104" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
       <c r="E104" s="7"/>
@@ -6379,8 +6923,12 @@
       <c r="AL104" s="7"/>
       <c r="AM104" s="7"/>
       <c r="AN104" s="7"/>
-    </row>
-    <row r="105" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO104" s="7"/>
+      <c r="AP104" s="7"/>
+      <c r="AQ104" s="7"/>
+      <c r="AR104" s="7"/>
+    </row>
+    <row r="105" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
@@ -6419,8 +6967,12 @@
       <c r="AL105" s="7"/>
       <c r="AM105" s="7"/>
       <c r="AN105" s="7"/>
-    </row>
-    <row r="106" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO105" s="7"/>
+      <c r="AP105" s="7"/>
+      <c r="AQ105" s="7"/>
+      <c r="AR105" s="7"/>
+    </row>
+    <row r="106" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
       <c r="E106" s="7"/>
@@ -6459,8 +7011,12 @@
       <c r="AL106" s="7"/>
       <c r="AM106" s="7"/>
       <c r="AN106" s="7"/>
-    </row>
-    <row r="107" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO106" s="7"/>
+      <c r="AP106" s="7"/>
+      <c r="AQ106" s="7"/>
+      <c r="AR106" s="7"/>
+    </row>
+    <row r="107" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
       <c r="E107" s="7"/>
@@ -6499,8 +7055,12 @@
       <c r="AL107" s="7"/>
       <c r="AM107" s="7"/>
       <c r="AN107" s="7"/>
-    </row>
-    <row r="108" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO107" s="7"/>
+      <c r="AP107" s="7"/>
+      <c r="AQ107" s="7"/>
+      <c r="AR107" s="7"/>
+    </row>
+    <row r="108" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
       <c r="E108" s="7"/>
@@ -6539,8 +7099,12 @@
       <c r="AL108" s="7"/>
       <c r="AM108" s="7"/>
       <c r="AN108" s="7"/>
-    </row>
-    <row r="109" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO108" s="7"/>
+      <c r="AP108" s="7"/>
+      <c r="AQ108" s="7"/>
+      <c r="AR108" s="7"/>
+    </row>
+    <row r="109" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C109" s="7"/>
       <c r="D109" s="7"/>
       <c r="E109" s="7"/>
@@ -6579,8 +7143,12 @@
       <c r="AL109" s="7"/>
       <c r="AM109" s="7"/>
       <c r="AN109" s="7"/>
-    </row>
-    <row r="110" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO109" s="7"/>
+      <c r="AP109" s="7"/>
+      <c r="AQ109" s="7"/>
+      <c r="AR109" s="7"/>
+    </row>
+    <row r="110" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7"/>
@@ -6619,8 +7187,12 @@
       <c r="AL110" s="7"/>
       <c r="AM110" s="7"/>
       <c r="AN110" s="7"/>
-    </row>
-    <row r="111" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO110" s="7"/>
+      <c r="AP110" s="7"/>
+      <c r="AQ110" s="7"/>
+      <c r="AR110" s="7"/>
+    </row>
+    <row r="111" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
       <c r="E111" s="7"/>
@@ -6659,8 +7231,12 @@
       <c r="AL111" s="7"/>
       <c r="AM111" s="7"/>
       <c r="AN111" s="7"/>
-    </row>
-    <row r="112" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO111" s="7"/>
+      <c r="AP111" s="7"/>
+      <c r="AQ111" s="7"/>
+      <c r="AR111" s="7"/>
+    </row>
+    <row r="112" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
       <c r="E112" s="7"/>
@@ -6699,8 +7275,12 @@
       <c r="AL112" s="7"/>
       <c r="AM112" s="7"/>
       <c r="AN112" s="7"/>
-    </row>
-    <row r="113" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO112" s="7"/>
+      <c r="AP112" s="7"/>
+      <c r="AQ112" s="7"/>
+      <c r="AR112" s="7"/>
+    </row>
+    <row r="113" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7"/>
@@ -6739,8 +7319,12 @@
       <c r="AL113" s="7"/>
       <c r="AM113" s="7"/>
       <c r="AN113" s="7"/>
-    </row>
-    <row r="114" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO113" s="7"/>
+      <c r="AP113" s="7"/>
+      <c r="AQ113" s="7"/>
+      <c r="AR113" s="7"/>
+    </row>
+    <row r="114" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7"/>
@@ -6779,8 +7363,12 @@
       <c r="AL114" s="7"/>
       <c r="AM114" s="7"/>
       <c r="AN114" s="7"/>
-    </row>
-    <row r="115" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO114" s="7"/>
+      <c r="AP114" s="7"/>
+      <c r="AQ114" s="7"/>
+      <c r="AR114" s="7"/>
+    </row>
+    <row r="115" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C115" s="7"/>
       <c r="D115" s="7"/>
       <c r="E115" s="7"/>
@@ -6819,8 +7407,12 @@
       <c r="AL115" s="7"/>
       <c r="AM115" s="7"/>
       <c r="AN115" s="7"/>
-    </row>
-    <row r="116" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO115" s="7"/>
+      <c r="AP115" s="7"/>
+      <c r="AQ115" s="7"/>
+      <c r="AR115" s="7"/>
+    </row>
+    <row r="116" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
       <c r="E116" s="7"/>
@@ -6859,8 +7451,12 @@
       <c r="AL116" s="7"/>
       <c r="AM116" s="7"/>
       <c r="AN116" s="7"/>
-    </row>
-    <row r="117" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO116" s="7"/>
+      <c r="AP116" s="7"/>
+      <c r="AQ116" s="7"/>
+      <c r="AR116" s="7"/>
+    </row>
+    <row r="117" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
       <c r="E117" s="7"/>
@@ -6899,8 +7495,12 @@
       <c r="AL117" s="7"/>
       <c r="AM117" s="7"/>
       <c r="AN117" s="7"/>
-    </row>
-    <row r="118" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO117" s="7"/>
+      <c r="AP117" s="7"/>
+      <c r="AQ117" s="7"/>
+      <c r="AR117" s="7"/>
+    </row>
+    <row r="118" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
       <c r="E118" s="7"/>
@@ -6939,8 +7539,12 @@
       <c r="AL118" s="7"/>
       <c r="AM118" s="7"/>
       <c r="AN118" s="7"/>
-    </row>
-    <row r="119" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO118" s="7"/>
+      <c r="AP118" s="7"/>
+      <c r="AQ118" s="7"/>
+      <c r="AR118" s="7"/>
+    </row>
+    <row r="119" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C119" s="7"/>
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
@@ -6979,8 +7583,12 @@
       <c r="AL119" s="7"/>
       <c r="AM119" s="7"/>
       <c r="AN119" s="7"/>
-    </row>
-    <row r="120" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO119" s="7"/>
+      <c r="AP119" s="7"/>
+      <c r="AQ119" s="7"/>
+      <c r="AR119" s="7"/>
+    </row>
+    <row r="120" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
       <c r="E120" s="7"/>
@@ -7019,8 +7627,12 @@
       <c r="AL120" s="7"/>
       <c r="AM120" s="7"/>
       <c r="AN120" s="7"/>
-    </row>
-    <row r="121" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO120" s="7"/>
+      <c r="AP120" s="7"/>
+      <c r="AQ120" s="7"/>
+      <c r="AR120" s="7"/>
+    </row>
+    <row r="121" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C121" s="7"/>
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
@@ -7059,8 +7671,12 @@
       <c r="AL121" s="7"/>
       <c r="AM121" s="7"/>
       <c r="AN121" s="7"/>
-    </row>
-    <row r="122" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO121" s="7"/>
+      <c r="AP121" s="7"/>
+      <c r="AQ121" s="7"/>
+      <c r="AR121" s="7"/>
+    </row>
+    <row r="122" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
       <c r="E122" s="7"/>
@@ -7099,8 +7715,12 @@
       <c r="AL122" s="7"/>
       <c r="AM122" s="7"/>
       <c r="AN122" s="7"/>
-    </row>
-    <row r="123" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO122" s="7"/>
+      <c r="AP122" s="7"/>
+      <c r="AQ122" s="7"/>
+      <c r="AR122" s="7"/>
+    </row>
+    <row r="123" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C123" s="7"/>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
@@ -7139,8 +7759,12 @@
       <c r="AL123" s="7"/>
       <c r="AM123" s="7"/>
       <c r="AN123" s="7"/>
-    </row>
-    <row r="124" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO123" s="7"/>
+      <c r="AP123" s="7"/>
+      <c r="AQ123" s="7"/>
+      <c r="AR123" s="7"/>
+    </row>
+    <row r="124" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
@@ -7179,8 +7803,12 @@
       <c r="AL124" s="7"/>
       <c r="AM124" s="7"/>
       <c r="AN124" s="7"/>
-    </row>
-    <row r="125" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO124" s="7"/>
+      <c r="AP124" s="7"/>
+      <c r="AQ124" s="7"/>
+      <c r="AR124" s="7"/>
+    </row>
+    <row r="125" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
@@ -7219,8 +7847,12 @@
       <c r="AL125" s="7"/>
       <c r="AM125" s="7"/>
       <c r="AN125" s="7"/>
-    </row>
-    <row r="126" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO125" s="7"/>
+      <c r="AP125" s="7"/>
+      <c r="AQ125" s="7"/>
+      <c r="AR125" s="7"/>
+    </row>
+    <row r="126" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
@@ -7259,8 +7891,12 @@
       <c r="AL126" s="7"/>
       <c r="AM126" s="7"/>
       <c r="AN126" s="7"/>
-    </row>
-    <row r="127" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO126" s="7"/>
+      <c r="AP126" s="7"/>
+      <c r="AQ126" s="7"/>
+      <c r="AR126" s="7"/>
+    </row>
+    <row r="127" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
@@ -7299,8 +7935,12 @@
       <c r="AL127" s="7"/>
       <c r="AM127" s="7"/>
       <c r="AN127" s="7"/>
-    </row>
-    <row r="128" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO127" s="7"/>
+      <c r="AP127" s="7"/>
+      <c r="AQ127" s="7"/>
+      <c r="AR127" s="7"/>
+    </row>
+    <row r="128" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
@@ -7339,8 +7979,12 @@
       <c r="AL128" s="7"/>
       <c r="AM128" s="7"/>
       <c r="AN128" s="7"/>
-    </row>
-    <row r="129" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO128" s="7"/>
+      <c r="AP128" s="7"/>
+      <c r="AQ128" s="7"/>
+      <c r="AR128" s="7"/>
+    </row>
+    <row r="129" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
@@ -7379,8 +8023,12 @@
       <c r="AL129" s="7"/>
       <c r="AM129" s="7"/>
       <c r="AN129" s="7"/>
-    </row>
-    <row r="130" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO129" s="7"/>
+      <c r="AP129" s="7"/>
+      <c r="AQ129" s="7"/>
+      <c r="AR129" s="7"/>
+    </row>
+    <row r="130" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
@@ -7419,8 +8067,12 @@
       <c r="AL130" s="7"/>
       <c r="AM130" s="7"/>
       <c r="AN130" s="7"/>
-    </row>
-    <row r="131" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO130" s="7"/>
+      <c r="AP130" s="7"/>
+      <c r="AQ130" s="7"/>
+      <c r="AR130" s="7"/>
+    </row>
+    <row r="131" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
@@ -7459,8 +8111,12 @@
       <c r="AL131" s="7"/>
       <c r="AM131" s="7"/>
       <c r="AN131" s="7"/>
-    </row>
-    <row r="132" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO131" s="7"/>
+      <c r="AP131" s="7"/>
+      <c r="AQ131" s="7"/>
+      <c r="AR131" s="7"/>
+    </row>
+    <row r="132" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7"/>
@@ -7499,8 +8155,12 @@
       <c r="AL132" s="7"/>
       <c r="AM132" s="7"/>
       <c r="AN132" s="7"/>
-    </row>
-    <row r="133" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO132" s="7"/>
+      <c r="AP132" s="7"/>
+      <c r="AQ132" s="7"/>
+      <c r="AR132" s="7"/>
+    </row>
+    <row r="133" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
@@ -7539,8 +8199,12 @@
       <c r="AL133" s="7"/>
       <c r="AM133" s="7"/>
       <c r="AN133" s="7"/>
-    </row>
-    <row r="134" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO133" s="7"/>
+      <c r="AP133" s="7"/>
+      <c r="AQ133" s="7"/>
+      <c r="AR133" s="7"/>
+    </row>
+    <row r="134" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
@@ -7579,8 +8243,12 @@
       <c r="AL134" s="7"/>
       <c r="AM134" s="7"/>
       <c r="AN134" s="7"/>
-    </row>
-    <row r="135" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO134" s="7"/>
+      <c r="AP134" s="7"/>
+      <c r="AQ134" s="7"/>
+      <c r="AR134" s="7"/>
+    </row>
+    <row r="135" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
@@ -7619,8 +8287,12 @@
       <c r="AL135" s="7"/>
       <c r="AM135" s="7"/>
       <c r="AN135" s="7"/>
-    </row>
-    <row r="136" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO135" s="7"/>
+      <c r="AP135" s="7"/>
+      <c r="AQ135" s="7"/>
+      <c r="AR135" s="7"/>
+    </row>
+    <row r="136" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
@@ -7659,8 +8331,12 @@
       <c r="AL136" s="7"/>
       <c r="AM136" s="7"/>
       <c r="AN136" s="7"/>
-    </row>
-    <row r="137" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO136" s="7"/>
+      <c r="AP136" s="7"/>
+      <c r="AQ136" s="7"/>
+      <c r="AR136" s="7"/>
+    </row>
+    <row r="137" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
@@ -7699,8 +8375,12 @@
       <c r="AL137" s="7"/>
       <c r="AM137" s="7"/>
       <c r="AN137" s="7"/>
-    </row>
-    <row r="138" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO137" s="7"/>
+      <c r="AP137" s="7"/>
+      <c r="AQ137" s="7"/>
+      <c r="AR137" s="7"/>
+    </row>
+    <row r="138" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
@@ -7739,8 +8419,12 @@
       <c r="AL138" s="7"/>
       <c r="AM138" s="7"/>
       <c r="AN138" s="7"/>
-    </row>
-    <row r="139" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO138" s="7"/>
+      <c r="AP138" s="7"/>
+      <c r="AQ138" s="7"/>
+      <c r="AR138" s="7"/>
+    </row>
+    <row r="139" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
@@ -7779,8 +8463,12 @@
       <c r="AL139" s="7"/>
       <c r="AM139" s="7"/>
       <c r="AN139" s="7"/>
-    </row>
-    <row r="140" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO139" s="7"/>
+      <c r="AP139" s="7"/>
+      <c r="AQ139" s="7"/>
+      <c r="AR139" s="7"/>
+    </row>
+    <row r="140" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7"/>
@@ -7819,8 +8507,12 @@
       <c r="AL140" s="7"/>
       <c r="AM140" s="7"/>
       <c r="AN140" s="7"/>
-    </row>
-    <row r="141" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO140" s="7"/>
+      <c r="AP140" s="7"/>
+      <c r="AQ140" s="7"/>
+      <c r="AR140" s="7"/>
+    </row>
+    <row r="141" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
@@ -7859,8 +8551,12 @@
       <c r="AL141" s="7"/>
       <c r="AM141" s="7"/>
       <c r="AN141" s="7"/>
-    </row>
-    <row r="142" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO141" s="7"/>
+      <c r="AP141" s="7"/>
+      <c r="AQ141" s="7"/>
+      <c r="AR141" s="7"/>
+    </row>
+    <row r="142" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7"/>
@@ -7899,8 +8595,12 @@
       <c r="AL142" s="7"/>
       <c r="AM142" s="7"/>
       <c r="AN142" s="7"/>
-    </row>
-    <row r="143" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO142" s="7"/>
+      <c r="AP142" s="7"/>
+      <c r="AQ142" s="7"/>
+      <c r="AR142" s="7"/>
+    </row>
+    <row r="143" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7"/>
@@ -7939,8 +8639,12 @@
       <c r="AL143" s="7"/>
       <c r="AM143" s="7"/>
       <c r="AN143" s="7"/>
-    </row>
-    <row r="144" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO143" s="7"/>
+      <c r="AP143" s="7"/>
+      <c r="AQ143" s="7"/>
+      <c r="AR143" s="7"/>
+    </row>
+    <row r="144" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C144" s="7"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7"/>
@@ -7979,8 +8683,12 @@
       <c r="AL144" s="7"/>
       <c r="AM144" s="7"/>
       <c r="AN144" s="7"/>
-    </row>
-    <row r="145" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO144" s="7"/>
+      <c r="AP144" s="7"/>
+      <c r="AQ144" s="7"/>
+      <c r="AR144" s="7"/>
+    </row>
+    <row r="145" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7"/>
@@ -8019,8 +8727,12 @@
       <c r="AL145" s="7"/>
       <c r="AM145" s="7"/>
       <c r="AN145" s="7"/>
-    </row>
-    <row r="146" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO145" s="7"/>
+      <c r="AP145" s="7"/>
+      <c r="AQ145" s="7"/>
+      <c r="AR145" s="7"/>
+    </row>
+    <row r="146" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C146" s="7"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7"/>
@@ -8059,8 +8771,12 @@
       <c r="AL146" s="7"/>
       <c r="AM146" s="7"/>
       <c r="AN146" s="7"/>
-    </row>
-    <row r="147" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO146" s="7"/>
+      <c r="AP146" s="7"/>
+      <c r="AQ146" s="7"/>
+      <c r="AR146" s="7"/>
+    </row>
+    <row r="147" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
@@ -8099,8 +8815,12 @@
       <c r="AL147" s="7"/>
       <c r="AM147" s="7"/>
       <c r="AN147" s="7"/>
-    </row>
-    <row r="148" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO147" s="7"/>
+      <c r="AP147" s="7"/>
+      <c r="AQ147" s="7"/>
+      <c r="AR147" s="7"/>
+    </row>
+    <row r="148" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C148" s="7"/>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
@@ -8139,8 +8859,12 @@
       <c r="AL148" s="7"/>
       <c r="AM148" s="7"/>
       <c r="AN148" s="7"/>
-    </row>
-    <row r="149" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO148" s="7"/>
+      <c r="AP148" s="7"/>
+      <c r="AQ148" s="7"/>
+      <c r="AR148" s="7"/>
+    </row>
+    <row r="149" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
@@ -8179,8 +8903,12 @@
       <c r="AL149" s="7"/>
       <c r="AM149" s="7"/>
       <c r="AN149" s="7"/>
-    </row>
-    <row r="150" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO149" s="7"/>
+      <c r="AP149" s="7"/>
+      <c r="AQ149" s="7"/>
+      <c r="AR149" s="7"/>
+    </row>
+    <row r="150" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C150" s="7"/>
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
@@ -8219,8 +8947,12 @@
       <c r="AL150" s="7"/>
       <c r="AM150" s="7"/>
       <c r="AN150" s="7"/>
-    </row>
-    <row r="151" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO150" s="7"/>
+      <c r="AP150" s="7"/>
+      <c r="AQ150" s="7"/>
+      <c r="AR150" s="7"/>
+    </row>
+    <row r="151" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
       <c r="E151" s="7"/>
@@ -8259,8 +8991,12 @@
       <c r="AL151" s="7"/>
       <c r="AM151" s="7"/>
       <c r="AN151" s="7"/>
-    </row>
-    <row r="152" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO151" s="7"/>
+      <c r="AP151" s="7"/>
+      <c r="AQ151" s="7"/>
+      <c r="AR151" s="7"/>
+    </row>
+    <row r="152" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C152" s="7"/>
       <c r="D152" s="7"/>
       <c r="E152" s="7"/>
@@ -8299,8 +9035,12 @@
       <c r="AL152" s="7"/>
       <c r="AM152" s="7"/>
       <c r="AN152" s="7"/>
-    </row>
-    <row r="153" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO152" s="7"/>
+      <c r="AP152" s="7"/>
+      <c r="AQ152" s="7"/>
+      <c r="AR152" s="7"/>
+    </row>
+    <row r="153" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C153" s="7"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7"/>
@@ -8339,8 +9079,12 @@
       <c r="AL153" s="7"/>
       <c r="AM153" s="7"/>
       <c r="AN153" s="7"/>
-    </row>
-    <row r="154" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO153" s="7"/>
+      <c r="AP153" s="7"/>
+      <c r="AQ153" s="7"/>
+      <c r="AR153" s="7"/>
+    </row>
+    <row r="154" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C154" s="7"/>
       <c r="D154" s="7"/>
       <c r="E154" s="7"/>
@@ -8379,8 +9123,12 @@
       <c r="AL154" s="7"/>
       <c r="AM154" s="7"/>
       <c r="AN154" s="7"/>
-    </row>
-    <row r="155" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO154" s="7"/>
+      <c r="AP154" s="7"/>
+      <c r="AQ154" s="7"/>
+      <c r="AR154" s="7"/>
+    </row>
+    <row r="155" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7"/>
@@ -8419,8 +9167,12 @@
       <c r="AL155" s="7"/>
       <c r="AM155" s="7"/>
       <c r="AN155" s="7"/>
-    </row>
-    <row r="156" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO155" s="7"/>
+      <c r="AP155" s="7"/>
+      <c r="AQ155" s="7"/>
+      <c r="AR155" s="7"/>
+    </row>
+    <row r="156" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
@@ -8459,8 +9211,12 @@
       <c r="AL156" s="7"/>
       <c r="AM156" s="7"/>
       <c r="AN156" s="7"/>
-    </row>
-    <row r="157" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO156" s="7"/>
+      <c r="AP156" s="7"/>
+      <c r="AQ156" s="7"/>
+      <c r="AR156" s="7"/>
+    </row>
+    <row r="157" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C157" s="7"/>
       <c r="D157" s="7"/>
       <c r="E157" s="7"/>
@@ -8499,8 +9255,12 @@
       <c r="AL157" s="7"/>
       <c r="AM157" s="7"/>
       <c r="AN157" s="7"/>
-    </row>
-    <row r="158" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO157" s="7"/>
+      <c r="AP157" s="7"/>
+      <c r="AQ157" s="7"/>
+      <c r="AR157" s="7"/>
+    </row>
+    <row r="158" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
@@ -8539,8 +9299,12 @@
       <c r="AL158" s="7"/>
       <c r="AM158" s="7"/>
       <c r="AN158" s="7"/>
-    </row>
-    <row r="159" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO158" s="7"/>
+      <c r="AP158" s="7"/>
+      <c r="AQ158" s="7"/>
+      <c r="AR158" s="7"/>
+    </row>
+    <row r="159" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
       <c r="E159" s="7"/>
@@ -8579,8 +9343,12 @@
       <c r="AL159" s="7"/>
       <c r="AM159" s="7"/>
       <c r="AN159" s="7"/>
-    </row>
-    <row r="160" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO159" s="7"/>
+      <c r="AP159" s="7"/>
+      <c r="AQ159" s="7"/>
+      <c r="AR159" s="7"/>
+    </row>
+    <row r="160" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7"/>
@@ -8619,8 +9387,12 @@
       <c r="AL160" s="7"/>
       <c r="AM160" s="7"/>
       <c r="AN160" s="7"/>
-    </row>
-    <row r="161" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO160" s="7"/>
+      <c r="AP160" s="7"/>
+      <c r="AQ160" s="7"/>
+      <c r="AR160" s="7"/>
+    </row>
+    <row r="161" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7"/>
@@ -8659,8 +9431,12 @@
       <c r="AL161" s="7"/>
       <c r="AM161" s="7"/>
       <c r="AN161" s="7"/>
-    </row>
-    <row r="162" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO161" s="7"/>
+      <c r="AP161" s="7"/>
+      <c r="AQ161" s="7"/>
+      <c r="AR161" s="7"/>
+    </row>
+    <row r="162" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
@@ -8699,8 +9475,12 @@
       <c r="AL162" s="7"/>
       <c r="AM162" s="7"/>
       <c r="AN162" s="7"/>
-    </row>
-    <row r="163" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO162" s="7"/>
+      <c r="AP162" s="7"/>
+      <c r="AQ162" s="7"/>
+      <c r="AR162" s="7"/>
+    </row>
+    <row r="163" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C163" s="7"/>
       <c r="D163" s="7"/>
       <c r="E163" s="7"/>
@@ -8739,8 +9519,12 @@
       <c r="AL163" s="7"/>
       <c r="AM163" s="7"/>
       <c r="AN163" s="7"/>
-    </row>
-    <row r="164" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO163" s="7"/>
+      <c r="AP163" s="7"/>
+      <c r="AQ163" s="7"/>
+      <c r="AR163" s="7"/>
+    </row>
+    <row r="164" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
@@ -8779,8 +9563,12 @@
       <c r="AL164" s="7"/>
       <c r="AM164" s="7"/>
       <c r="AN164" s="7"/>
-    </row>
-    <row r="165" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO164" s="7"/>
+      <c r="AP164" s="7"/>
+      <c r="AQ164" s="7"/>
+      <c r="AR164" s="7"/>
+    </row>
+    <row r="165" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7"/>
@@ -8819,8 +9607,12 @@
       <c r="AL165" s="7"/>
       <c r="AM165" s="7"/>
       <c r="AN165" s="7"/>
-    </row>
-    <row r="166" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO165" s="7"/>
+      <c r="AP165" s="7"/>
+      <c r="AQ165" s="7"/>
+      <c r="AR165" s="7"/>
+    </row>
+    <row r="166" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7"/>
@@ -8859,8 +9651,12 @@
       <c r="AL166" s="7"/>
       <c r="AM166" s="7"/>
       <c r="AN166" s="7"/>
-    </row>
-    <row r="167" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO166" s="7"/>
+      <c r="AP166" s="7"/>
+      <c r="AQ166" s="7"/>
+      <c r="AR166" s="7"/>
+    </row>
+    <row r="167" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
       <c r="E167" s="7"/>
@@ -8899,8 +9695,12 @@
       <c r="AL167" s="7"/>
       <c r="AM167" s="7"/>
       <c r="AN167" s="7"/>
-    </row>
-    <row r="168" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO167" s="7"/>
+      <c r="AP167" s="7"/>
+      <c r="AQ167" s="7"/>
+      <c r="AR167" s="7"/>
+    </row>
+    <row r="168" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
@@ -8939,8 +9739,12 @@
       <c r="AL168" s="7"/>
       <c r="AM168" s="7"/>
       <c r="AN168" s="7"/>
-    </row>
-    <row r="169" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO168" s="7"/>
+      <c r="AP168" s="7"/>
+      <c r="AQ168" s="7"/>
+      <c r="AR168" s="7"/>
+    </row>
+    <row r="169" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
@@ -8979,8 +9783,12 @@
       <c r="AL169" s="7"/>
       <c r="AM169" s="7"/>
       <c r="AN169" s="7"/>
-    </row>
-    <row r="170" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO169" s="7"/>
+      <c r="AP169" s="7"/>
+      <c r="AQ169" s="7"/>
+      <c r="AR169" s="7"/>
+    </row>
+    <row r="170" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
@@ -9019,8 +9827,12 @@
       <c r="AL170" s="7"/>
       <c r="AM170" s="7"/>
       <c r="AN170" s="7"/>
-    </row>
-    <row r="171" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO170" s="7"/>
+      <c r="AP170" s="7"/>
+      <c r="AQ170" s="7"/>
+      <c r="AR170" s="7"/>
+    </row>
+    <row r="171" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
@@ -9059,8 +9871,12 @@
       <c r="AL171" s="7"/>
       <c r="AM171" s="7"/>
       <c r="AN171" s="7"/>
-    </row>
-    <row r="172" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO171" s="7"/>
+      <c r="AP171" s="7"/>
+      <c r="AQ171" s="7"/>
+      <c r="AR171" s="7"/>
+    </row>
+    <row r="172" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
@@ -9099,8 +9915,12 @@
       <c r="AL172" s="7"/>
       <c r="AM172" s="7"/>
       <c r="AN172" s="7"/>
-    </row>
-    <row r="173" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO172" s="7"/>
+      <c r="AP172" s="7"/>
+      <c r="AQ172" s="7"/>
+      <c r="AR172" s="7"/>
+    </row>
+    <row r="173" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7"/>
@@ -9139,8 +9959,12 @@
       <c r="AL173" s="7"/>
       <c r="AM173" s="7"/>
       <c r="AN173" s="7"/>
-    </row>
-    <row r="174" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO173" s="7"/>
+      <c r="AP173" s="7"/>
+      <c r="AQ173" s="7"/>
+      <c r="AR173" s="7"/>
+    </row>
+    <row r="174" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7"/>
@@ -9179,8 +10003,12 @@
       <c r="AL174" s="7"/>
       <c r="AM174" s="7"/>
       <c r="AN174" s="7"/>
-    </row>
-    <row r="175" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO174" s="7"/>
+      <c r="AP174" s="7"/>
+      <c r="AQ174" s="7"/>
+      <c r="AR174" s="7"/>
+    </row>
+    <row r="175" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
@@ -9219,8 +10047,12 @@
       <c r="AL175" s="7"/>
       <c r="AM175" s="7"/>
       <c r="AN175" s="7"/>
-    </row>
-    <row r="176" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO175" s="7"/>
+      <c r="AP175" s="7"/>
+      <c r="AQ175" s="7"/>
+      <c r="AR175" s="7"/>
+    </row>
+    <row r="176" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7"/>
@@ -9259,8 +10091,12 @@
       <c r="AL176" s="7"/>
       <c r="AM176" s="7"/>
       <c r="AN176" s="7"/>
-    </row>
-    <row r="177" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO176" s="7"/>
+      <c r="AP176" s="7"/>
+      <c r="AQ176" s="7"/>
+      <c r="AR176" s="7"/>
+    </row>
+    <row r="177" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7"/>
@@ -9299,8 +10135,12 @@
       <c r="AL177" s="7"/>
       <c r="AM177" s="7"/>
       <c r="AN177" s="7"/>
-    </row>
-    <row r="178" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO177" s="7"/>
+      <c r="AP177" s="7"/>
+      <c r="AQ177" s="7"/>
+      <c r="AR177" s="7"/>
+    </row>
+    <row r="178" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7"/>
@@ -9339,8 +10179,12 @@
       <c r="AL178" s="7"/>
       <c r="AM178" s="7"/>
       <c r="AN178" s="7"/>
-    </row>
-    <row r="179" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO178" s="7"/>
+      <c r="AP178" s="7"/>
+      <c r="AQ178" s="7"/>
+      <c r="AR178" s="7"/>
+    </row>
+    <row r="179" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7"/>
@@ -9379,8 +10223,12 @@
       <c r="AL179" s="7"/>
       <c r="AM179" s="7"/>
       <c r="AN179" s="7"/>
-    </row>
-    <row r="180" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO179" s="7"/>
+      <c r="AP179" s="7"/>
+      <c r="AQ179" s="7"/>
+      <c r="AR179" s="7"/>
+    </row>
+    <row r="180" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7"/>
@@ -9419,8 +10267,12 @@
       <c r="AL180" s="7"/>
       <c r="AM180" s="7"/>
       <c r="AN180" s="7"/>
-    </row>
-    <row r="181" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO180" s="7"/>
+      <c r="AP180" s="7"/>
+      <c r="AQ180" s="7"/>
+      <c r="AR180" s="7"/>
+    </row>
+    <row r="181" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7"/>
@@ -9459,8 +10311,12 @@
       <c r="AL181" s="7"/>
       <c r="AM181" s="7"/>
       <c r="AN181" s="7"/>
-    </row>
-    <row r="182" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO181" s="7"/>
+      <c r="AP181" s="7"/>
+      <c r="AQ181" s="7"/>
+      <c r="AR181" s="7"/>
+    </row>
+    <row r="182" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7"/>
@@ -9499,8 +10355,12 @@
       <c r="AL182" s="7"/>
       <c r="AM182" s="7"/>
       <c r="AN182" s="7"/>
-    </row>
-    <row r="183" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO182" s="7"/>
+      <c r="AP182" s="7"/>
+      <c r="AQ182" s="7"/>
+      <c r="AR182" s="7"/>
+    </row>
+    <row r="183" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7"/>
@@ -9539,8 +10399,12 @@
       <c r="AL183" s="7"/>
       <c r="AM183" s="7"/>
       <c r="AN183" s="7"/>
-    </row>
-    <row r="184" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO183" s="7"/>
+      <c r="AP183" s="7"/>
+      <c r="AQ183" s="7"/>
+      <c r="AR183" s="7"/>
+    </row>
+    <row r="184" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
@@ -9579,8 +10443,12 @@
       <c r="AL184" s="7"/>
       <c r="AM184" s="7"/>
       <c r="AN184" s="7"/>
-    </row>
-    <row r="185" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO184" s="7"/>
+      <c r="AP184" s="7"/>
+      <c r="AQ184" s="7"/>
+      <c r="AR184" s="7"/>
+    </row>
+    <row r="185" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
       <c r="E185" s="7"/>
@@ -9619,8 +10487,12 @@
       <c r="AL185" s="7"/>
       <c r="AM185" s="7"/>
       <c r="AN185" s="7"/>
-    </row>
-    <row r="186" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO185" s="7"/>
+      <c r="AP185" s="7"/>
+      <c r="AQ185" s="7"/>
+      <c r="AR185" s="7"/>
+    </row>
+    <row r="186" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
@@ -9659,8 +10531,12 @@
       <c r="AL186" s="7"/>
       <c r="AM186" s="7"/>
       <c r="AN186" s="7"/>
-    </row>
-    <row r="187" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO186" s="7"/>
+      <c r="AP186" s="7"/>
+      <c r="AQ186" s="7"/>
+      <c r="AR186" s="7"/>
+    </row>
+    <row r="187" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7"/>
@@ -9699,8 +10575,12 @@
       <c r="AL187" s="7"/>
       <c r="AM187" s="7"/>
       <c r="AN187" s="7"/>
-    </row>
-    <row r="188" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO187" s="7"/>
+      <c r="AP187" s="7"/>
+      <c r="AQ187" s="7"/>
+      <c r="AR187" s="7"/>
+    </row>
+    <row r="188" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7"/>
@@ -9739,8 +10619,12 @@
       <c r="AL188" s="7"/>
       <c r="AM188" s="7"/>
       <c r="AN188" s="7"/>
-    </row>
-    <row r="189" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO188" s="7"/>
+      <c r="AP188" s="7"/>
+      <c r="AQ188" s="7"/>
+      <c r="AR188" s="7"/>
+    </row>
+    <row r="189" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
       <c r="E189" s="7"/>
@@ -9779,8 +10663,12 @@
       <c r="AL189" s="7"/>
       <c r="AM189" s="7"/>
       <c r="AN189" s="7"/>
-    </row>
-    <row r="190" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO189" s="7"/>
+      <c r="AP189" s="7"/>
+      <c r="AQ189" s="7"/>
+      <c r="AR189" s="7"/>
+    </row>
+    <row r="190" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7"/>
@@ -9819,8 +10707,12 @@
       <c r="AL190" s="7"/>
       <c r="AM190" s="7"/>
       <c r="AN190" s="7"/>
-    </row>
-    <row r="191" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO190" s="7"/>
+      <c r="AP190" s="7"/>
+      <c r="AQ190" s="7"/>
+      <c r="AR190" s="7"/>
+    </row>
+    <row r="191" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
       <c r="E191" s="7"/>
@@ -9859,8 +10751,12 @@
       <c r="AL191" s="7"/>
       <c r="AM191" s="7"/>
       <c r="AN191" s="7"/>
-    </row>
-    <row r="192" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO191" s="7"/>
+      <c r="AP191" s="7"/>
+      <c r="AQ191" s="7"/>
+      <c r="AR191" s="7"/>
+    </row>
+    <row r="192" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7"/>
@@ -9899,8 +10795,12 @@
       <c r="AL192" s="7"/>
       <c r="AM192" s="7"/>
       <c r="AN192" s="7"/>
-    </row>
-    <row r="193" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO192" s="7"/>
+      <c r="AP192" s="7"/>
+      <c r="AQ192" s="7"/>
+      <c r="AR192" s="7"/>
+    </row>
+    <row r="193" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C193" s="7"/>
       <c r="D193" s="7"/>
       <c r="E193" s="7"/>
@@ -9939,8 +10839,12 @@
       <c r="AL193" s="7"/>
       <c r="AM193" s="7"/>
       <c r="AN193" s="7"/>
-    </row>
-    <row r="194" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO193" s="7"/>
+      <c r="AP193" s="7"/>
+      <c r="AQ193" s="7"/>
+      <c r="AR193" s="7"/>
+    </row>
+    <row r="194" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
       <c r="E194" s="7"/>
@@ -9979,8 +10883,12 @@
       <c r="AL194" s="7"/>
       <c r="AM194" s="7"/>
       <c r="AN194" s="7"/>
-    </row>
-    <row r="195" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO194" s="7"/>
+      <c r="AP194" s="7"/>
+      <c r="AQ194" s="7"/>
+      <c r="AR194" s="7"/>
+    </row>
+    <row r="195" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C195" s="7"/>
       <c r="D195" s="7"/>
       <c r="E195" s="7"/>
@@ -10019,8 +10927,12 @@
       <c r="AL195" s="7"/>
       <c r="AM195" s="7"/>
       <c r="AN195" s="7"/>
-    </row>
-    <row r="196" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO195" s="7"/>
+      <c r="AP195" s="7"/>
+      <c r="AQ195" s="7"/>
+      <c r="AR195" s="7"/>
+    </row>
+    <row r="196" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
       <c r="E196" s="7"/>
@@ -10059,8 +10971,12 @@
       <c r="AL196" s="7"/>
       <c r="AM196" s="7"/>
       <c r="AN196" s="7"/>
-    </row>
-    <row r="197" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO196" s="7"/>
+      <c r="AP196" s="7"/>
+      <c r="AQ196" s="7"/>
+      <c r="AR196" s="7"/>
+    </row>
+    <row r="197" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C197" s="7"/>
       <c r="D197" s="7"/>
       <c r="E197" s="7"/>
@@ -10099,8 +11015,12 @@
       <c r="AL197" s="7"/>
       <c r="AM197" s="7"/>
       <c r="AN197" s="7"/>
-    </row>
-    <row r="198" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO197" s="7"/>
+      <c r="AP197" s="7"/>
+      <c r="AQ197" s="7"/>
+      <c r="AR197" s="7"/>
+    </row>
+    <row r="198" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
       <c r="E198" s="7"/>
@@ -10139,8 +11059,12 @@
       <c r="AL198" s="7"/>
       <c r="AM198" s="7"/>
       <c r="AN198" s="7"/>
-    </row>
-    <row r="199" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO198" s="7"/>
+      <c r="AP198" s="7"/>
+      <c r="AQ198" s="7"/>
+      <c r="AR198" s="7"/>
+    </row>
+    <row r="199" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C199" s="7"/>
       <c r="D199" s="7"/>
       <c r="E199" s="7"/>
@@ -10179,8 +11103,12 @@
       <c r="AL199" s="7"/>
       <c r="AM199" s="7"/>
       <c r="AN199" s="7"/>
-    </row>
-    <row r="200" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO199" s="7"/>
+      <c r="AP199" s="7"/>
+      <c r="AQ199" s="7"/>
+      <c r="AR199" s="7"/>
+    </row>
+    <row r="200" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
       <c r="E200" s="7"/>
@@ -10219,8 +11147,12 @@
       <c r="AL200" s="7"/>
       <c r="AM200" s="7"/>
       <c r="AN200" s="7"/>
-    </row>
-    <row r="201" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO200" s="7"/>
+      <c r="AP200" s="7"/>
+      <c r="AQ200" s="7"/>
+      <c r="AR200" s="7"/>
+    </row>
+    <row r="201" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C201" s="7"/>
       <c r="D201" s="7"/>
       <c r="E201" s="7"/>
@@ -10259,8 +11191,12 @@
       <c r="AL201" s="7"/>
       <c r="AM201" s="7"/>
       <c r="AN201" s="7"/>
-    </row>
-    <row r="202" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO201" s="7"/>
+      <c r="AP201" s="7"/>
+      <c r="AQ201" s="7"/>
+      <c r="AR201" s="7"/>
+    </row>
+    <row r="202" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C202" s="7"/>
       <c r="D202" s="7"/>
       <c r="E202" s="7"/>
@@ -10299,8 +11235,12 @@
       <c r="AL202" s="7"/>
       <c r="AM202" s="7"/>
       <c r="AN202" s="7"/>
-    </row>
-    <row r="203" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO202" s="7"/>
+      <c r="AP202" s="7"/>
+      <c r="AQ202" s="7"/>
+      <c r="AR202" s="7"/>
+    </row>
+    <row r="203" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C203" s="7"/>
       <c r="D203" s="7"/>
       <c r="E203" s="7"/>
@@ -10339,8 +11279,12 @@
       <c r="AL203" s="7"/>
       <c r="AM203" s="7"/>
       <c r="AN203" s="7"/>
-    </row>
-    <row r="204" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO203" s="7"/>
+      <c r="AP203" s="7"/>
+      <c r="AQ203" s="7"/>
+      <c r="AR203" s="7"/>
+    </row>
+    <row r="204" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
       <c r="E204" s="7"/>
@@ -10379,8 +11323,12 @@
       <c r="AL204" s="7"/>
       <c r="AM204" s="7"/>
       <c r="AN204" s="7"/>
-    </row>
-    <row r="205" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO204" s="7"/>
+      <c r="AP204" s="7"/>
+      <c r="AQ204" s="7"/>
+      <c r="AR204" s="7"/>
+    </row>
+    <row r="205" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
       <c r="E205" s="7"/>
@@ -10419,8 +11367,12 @@
       <c r="AL205" s="7"/>
       <c r="AM205" s="7"/>
       <c r="AN205" s="7"/>
-    </row>
-    <row r="206" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO205" s="7"/>
+      <c r="AP205" s="7"/>
+      <c r="AQ205" s="7"/>
+      <c r="AR205" s="7"/>
+    </row>
+    <row r="206" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
       <c r="E206" s="7"/>
@@ -10459,8 +11411,12 @@
       <c r="AL206" s="7"/>
       <c r="AM206" s="7"/>
       <c r="AN206" s="7"/>
-    </row>
-    <row r="207" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO206" s="7"/>
+      <c r="AP206" s="7"/>
+      <c r="AQ206" s="7"/>
+      <c r="AR206" s="7"/>
+    </row>
+    <row r="207" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
       <c r="E207" s="7"/>
@@ -10499,8 +11455,12 @@
       <c r="AL207" s="7"/>
       <c r="AM207" s="7"/>
       <c r="AN207" s="7"/>
-    </row>
-    <row r="208" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO207" s="7"/>
+      <c r="AP207" s="7"/>
+      <c r="AQ207" s="7"/>
+      <c r="AR207" s="7"/>
+    </row>
+    <row r="208" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
       <c r="E208" s="7"/>
@@ -10539,8 +11499,12 @@
       <c r="AL208" s="7"/>
       <c r="AM208" s="7"/>
       <c r="AN208" s="7"/>
-    </row>
-    <row r="209" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO208" s="7"/>
+      <c r="AP208" s="7"/>
+      <c r="AQ208" s="7"/>
+      <c r="AR208" s="7"/>
+    </row>
+    <row r="209" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
       <c r="E209" s="7"/>
@@ -10579,8 +11543,12 @@
       <c r="AL209" s="7"/>
       <c r="AM209" s="7"/>
       <c r="AN209" s="7"/>
-    </row>
-    <row r="210" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO209" s="7"/>
+      <c r="AP209" s="7"/>
+      <c r="AQ209" s="7"/>
+      <c r="AR209" s="7"/>
+    </row>
+    <row r="210" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
       <c r="E210" s="7"/>
@@ -10619,8 +11587,12 @@
       <c r="AL210" s="7"/>
       <c r="AM210" s="7"/>
       <c r="AN210" s="7"/>
-    </row>
-    <row r="211" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO210" s="7"/>
+      <c r="AP210" s="7"/>
+      <c r="AQ210" s="7"/>
+      <c r="AR210" s="7"/>
+    </row>
+    <row r="211" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
       <c r="E211" s="7"/>
@@ -10659,8 +11631,12 @@
       <c r="AL211" s="7"/>
       <c r="AM211" s="7"/>
       <c r="AN211" s="7"/>
-    </row>
-    <row r="212" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO211" s="7"/>
+      <c r="AP211" s="7"/>
+      <c r="AQ211" s="7"/>
+      <c r="AR211" s="7"/>
+    </row>
+    <row r="212" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C212" s="7"/>
       <c r="D212" s="7"/>
       <c r="E212" s="7"/>
@@ -10699,8 +11675,12 @@
       <c r="AL212" s="7"/>
       <c r="AM212" s="7"/>
       <c r="AN212" s="7"/>
-    </row>
-    <row r="213" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO212" s="7"/>
+      <c r="AP212" s="7"/>
+      <c r="AQ212" s="7"/>
+      <c r="AR212" s="7"/>
+    </row>
+    <row r="213" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C213" s="7"/>
       <c r="D213" s="7"/>
       <c r="E213" s="7"/>
@@ -10739,8 +11719,12 @@
       <c r="AL213" s="7"/>
       <c r="AM213" s="7"/>
       <c r="AN213" s="7"/>
-    </row>
-    <row r="214" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO213" s="7"/>
+      <c r="AP213" s="7"/>
+      <c r="AQ213" s="7"/>
+      <c r="AR213" s="7"/>
+    </row>
+    <row r="214" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C214" s="7"/>
       <c r="D214" s="7"/>
       <c r="E214" s="7"/>
@@ -10779,8 +11763,12 @@
       <c r="AL214" s="7"/>
       <c r="AM214" s="7"/>
       <c r="AN214" s="7"/>
-    </row>
-    <row r="215" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO214" s="7"/>
+      <c r="AP214" s="7"/>
+      <c r="AQ214" s="7"/>
+      <c r="AR214" s="7"/>
+    </row>
+    <row r="215" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C215" s="7"/>
       <c r="D215" s="7"/>
       <c r="E215" s="7"/>
@@ -10819,8 +11807,12 @@
       <c r="AL215" s="7"/>
       <c r="AM215" s="7"/>
       <c r="AN215" s="7"/>
-    </row>
-    <row r="216" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO215" s="7"/>
+      <c r="AP215" s="7"/>
+      <c r="AQ215" s="7"/>
+      <c r="AR215" s="7"/>
+    </row>
+    <row r="216" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C216" s="7"/>
       <c r="D216" s="7"/>
       <c r="E216" s="7"/>
@@ -10859,8 +11851,12 @@
       <c r="AL216" s="7"/>
       <c r="AM216" s="7"/>
       <c r="AN216" s="7"/>
-    </row>
-    <row r="217" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO216" s="7"/>
+      <c r="AP216" s="7"/>
+      <c r="AQ216" s="7"/>
+      <c r="AR216" s="7"/>
+    </row>
+    <row r="217" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
       <c r="E217" s="7"/>
@@ -10899,8 +11895,12 @@
       <c r="AL217" s="7"/>
       <c r="AM217" s="7"/>
       <c r="AN217" s="7"/>
-    </row>
-    <row r="218" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO217" s="7"/>
+      <c r="AP217" s="7"/>
+      <c r="AQ217" s="7"/>
+      <c r="AR217" s="7"/>
+    </row>
+    <row r="218" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
       <c r="E218" s="7"/>
@@ -10939,8 +11939,12 @@
       <c r="AL218" s="7"/>
       <c r="AM218" s="7"/>
       <c r="AN218" s="7"/>
-    </row>
-    <row r="219" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO218" s="7"/>
+      <c r="AP218" s="7"/>
+      <c r="AQ218" s="7"/>
+      <c r="AR218" s="7"/>
+    </row>
+    <row r="219" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
       <c r="E219" s="7"/>
@@ -10979,8 +11983,12 @@
       <c r="AL219" s="7"/>
       <c r="AM219" s="7"/>
       <c r="AN219" s="7"/>
-    </row>
-    <row r="220" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO219" s="7"/>
+      <c r="AP219" s="7"/>
+      <c r="AQ219" s="7"/>
+      <c r="AR219" s="7"/>
+    </row>
+    <row r="220" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
       <c r="E220" s="7"/>
@@ -11019,8 +12027,12 @@
       <c r="AL220" s="7"/>
       <c r="AM220" s="7"/>
       <c r="AN220" s="7"/>
-    </row>
-    <row r="221" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO220" s="7"/>
+      <c r="AP220" s="7"/>
+      <c r="AQ220" s="7"/>
+      <c r="AR220" s="7"/>
+    </row>
+    <row r="221" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
       <c r="E221" s="7"/>
@@ -11059,8 +12071,12 @@
       <c r="AL221" s="7"/>
       <c r="AM221" s="7"/>
       <c r="AN221" s="7"/>
-    </row>
-    <row r="222" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO221" s="7"/>
+      <c r="AP221" s="7"/>
+      <c r="AQ221" s="7"/>
+      <c r="AR221" s="7"/>
+    </row>
+    <row r="222" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
       <c r="E222" s="7"/>
@@ -11099,8 +12115,12 @@
       <c r="AL222" s="7"/>
       <c r="AM222" s="7"/>
       <c r="AN222" s="7"/>
-    </row>
-    <row r="223" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO222" s="7"/>
+      <c r="AP222" s="7"/>
+      <c r="AQ222" s="7"/>
+      <c r="AR222" s="7"/>
+    </row>
+    <row r="223" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
       <c r="E223" s="7"/>
@@ -11139,8 +12159,12 @@
       <c r="AL223" s="7"/>
       <c r="AM223" s="7"/>
       <c r="AN223" s="7"/>
-    </row>
-    <row r="224" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO223" s="7"/>
+      <c r="AP223" s="7"/>
+      <c r="AQ223" s="7"/>
+      <c r="AR223" s="7"/>
+    </row>
+    <row r="224" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C224" s="7"/>
       <c r="D224" s="7"/>
       <c r="E224" s="7"/>
@@ -11179,8 +12203,12 @@
       <c r="AL224" s="7"/>
       <c r="AM224" s="7"/>
       <c r="AN224" s="7"/>
-    </row>
-    <row r="225" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO224" s="7"/>
+      <c r="AP224" s="7"/>
+      <c r="AQ224" s="7"/>
+      <c r="AR224" s="7"/>
+    </row>
+    <row r="225" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C225" s="7"/>
       <c r="D225" s="7"/>
       <c r="E225" s="7"/>
@@ -11219,8 +12247,12 @@
       <c r="AL225" s="7"/>
       <c r="AM225" s="7"/>
       <c r="AN225" s="7"/>
-    </row>
-    <row r="226" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO225" s="7"/>
+      <c r="AP225" s="7"/>
+      <c r="AQ225" s="7"/>
+      <c r="AR225" s="7"/>
+    </row>
+    <row r="226" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C226" s="7"/>
       <c r="D226" s="7"/>
       <c r="E226" s="7"/>
@@ -11259,8 +12291,12 @@
       <c r="AL226" s="7"/>
       <c r="AM226" s="7"/>
       <c r="AN226" s="7"/>
-    </row>
-    <row r="227" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO226" s="7"/>
+      <c r="AP226" s="7"/>
+      <c r="AQ226" s="7"/>
+      <c r="AR226" s="7"/>
+    </row>
+    <row r="227" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C227" s="7"/>
       <c r="D227" s="7"/>
       <c r="E227" s="7"/>
@@ -11299,8 +12335,12 @@
       <c r="AL227" s="7"/>
       <c r="AM227" s="7"/>
       <c r="AN227" s="7"/>
-    </row>
-    <row r="228" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO227" s="7"/>
+      <c r="AP227" s="7"/>
+      <c r="AQ227" s="7"/>
+      <c r="AR227" s="7"/>
+    </row>
+    <row r="228" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
       <c r="E228" s="7"/>
@@ -11339,8 +12379,12 @@
       <c r="AL228" s="7"/>
       <c r="AM228" s="7"/>
       <c r="AN228" s="7"/>
-    </row>
-    <row r="229" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO228" s="7"/>
+      <c r="AP228" s="7"/>
+      <c r="AQ228" s="7"/>
+      <c r="AR228" s="7"/>
+    </row>
+    <row r="229" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
       <c r="E229" s="7"/>
@@ -11379,8 +12423,12 @@
       <c r="AL229" s="7"/>
       <c r="AM229" s="7"/>
       <c r="AN229" s="7"/>
-    </row>
-    <row r="230" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO229" s="7"/>
+      <c r="AP229" s="7"/>
+      <c r="AQ229" s="7"/>
+      <c r="AR229" s="7"/>
+    </row>
+    <row r="230" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
       <c r="E230" s="7"/>
@@ -11419,8 +12467,12 @@
       <c r="AL230" s="7"/>
       <c r="AM230" s="7"/>
       <c r="AN230" s="7"/>
-    </row>
-    <row r="231" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO230" s="7"/>
+      <c r="AP230" s="7"/>
+      <c r="AQ230" s="7"/>
+      <c r="AR230" s="7"/>
+    </row>
+    <row r="231" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C231" s="7"/>
       <c r="D231" s="7"/>
       <c r="E231" s="7"/>
@@ -11459,8 +12511,12 @@
       <c r="AL231" s="7"/>
       <c r="AM231" s="7"/>
       <c r="AN231" s="7"/>
-    </row>
-    <row r="232" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO231" s="7"/>
+      <c r="AP231" s="7"/>
+      <c r="AQ231" s="7"/>
+      <c r="AR231" s="7"/>
+    </row>
+    <row r="232" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
       <c r="E232" s="7"/>
@@ -11499,8 +12555,12 @@
       <c r="AL232" s="7"/>
       <c r="AM232" s="7"/>
       <c r="AN232" s="7"/>
-    </row>
-    <row r="233" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO232" s="7"/>
+      <c r="AP232" s="7"/>
+      <c r="AQ232" s="7"/>
+      <c r="AR232" s="7"/>
+    </row>
+    <row r="233" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
       <c r="E233" s="7"/>
@@ -11539,8 +12599,12 @@
       <c r="AL233" s="7"/>
       <c r="AM233" s="7"/>
       <c r="AN233" s="7"/>
-    </row>
-    <row r="234" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO233" s="7"/>
+      <c r="AP233" s="7"/>
+      <c r="AQ233" s="7"/>
+      <c r="AR233" s="7"/>
+    </row>
+    <row r="234" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C234" s="7"/>
       <c r="D234" s="7"/>
       <c r="E234" s="7"/>
@@ -11579,8 +12643,12 @@
       <c r="AL234" s="7"/>
       <c r="AM234" s="7"/>
       <c r="AN234" s="7"/>
-    </row>
-    <row r="235" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO234" s="7"/>
+      <c r="AP234" s="7"/>
+      <c r="AQ234" s="7"/>
+      <c r="AR234" s="7"/>
+    </row>
+    <row r="235" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C235" s="7"/>
       <c r="D235" s="7"/>
       <c r="E235" s="7"/>
@@ -11619,8 +12687,12 @@
       <c r="AL235" s="7"/>
       <c r="AM235" s="7"/>
       <c r="AN235" s="7"/>
-    </row>
-    <row r="236" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO235" s="7"/>
+      <c r="AP235" s="7"/>
+      <c r="AQ235" s="7"/>
+      <c r="AR235" s="7"/>
+    </row>
+    <row r="236" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C236" s="7"/>
       <c r="D236" s="7"/>
       <c r="E236" s="7"/>
@@ -11659,8 +12731,12 @@
       <c r="AL236" s="7"/>
       <c r="AM236" s="7"/>
       <c r="AN236" s="7"/>
-    </row>
-    <row r="237" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO236" s="7"/>
+      <c r="AP236" s="7"/>
+      <c r="AQ236" s="7"/>
+      <c r="AR236" s="7"/>
+    </row>
+    <row r="237" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
       <c r="E237" s="7"/>
@@ -11699,8 +12775,12 @@
       <c r="AL237" s="7"/>
       <c r="AM237" s="7"/>
       <c r="AN237" s="7"/>
-    </row>
-    <row r="238" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO237" s="7"/>
+      <c r="AP237" s="7"/>
+      <c r="AQ237" s="7"/>
+      <c r="AR237" s="7"/>
+    </row>
+    <row r="238" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C238" s="7"/>
       <c r="D238" s="7"/>
       <c r="E238" s="7"/>
@@ -11739,8 +12819,12 @@
       <c r="AL238" s="7"/>
       <c r="AM238" s="7"/>
       <c r="AN238" s="7"/>
-    </row>
-    <row r="239" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO238" s="7"/>
+      <c r="AP238" s="7"/>
+      <c r="AQ238" s="7"/>
+      <c r="AR238" s="7"/>
+    </row>
+    <row r="239" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C239" s="7"/>
       <c r="D239" s="7"/>
       <c r="E239" s="7"/>
@@ -11779,8 +12863,12 @@
       <c r="AL239" s="7"/>
       <c r="AM239" s="7"/>
       <c r="AN239" s="7"/>
-    </row>
-    <row r="240" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO239" s="7"/>
+      <c r="AP239" s="7"/>
+      <c r="AQ239" s="7"/>
+      <c r="AR239" s="7"/>
+    </row>
+    <row r="240" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C240" s="7"/>
       <c r="D240" s="7"/>
       <c r="E240" s="7"/>
@@ -11819,8 +12907,12 @@
       <c r="AL240" s="7"/>
       <c r="AM240" s="7"/>
       <c r="AN240" s="7"/>
-    </row>
-    <row r="241" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO240" s="7"/>
+      <c r="AP240" s="7"/>
+      <c r="AQ240" s="7"/>
+      <c r="AR240" s="7"/>
+    </row>
+    <row r="241" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C241" s="7"/>
       <c r="D241" s="7"/>
       <c r="E241" s="7"/>
@@ -11859,8 +12951,12 @@
       <c r="AL241" s="7"/>
       <c r="AM241" s="7"/>
       <c r="AN241" s="7"/>
-    </row>
-    <row r="242" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO241" s="7"/>
+      <c r="AP241" s="7"/>
+      <c r="AQ241" s="7"/>
+      <c r="AR241" s="7"/>
+    </row>
+    <row r="242" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C242" s="7"/>
       <c r="D242" s="7"/>
       <c r="E242" s="7"/>
@@ -11899,8 +12995,12 @@
       <c r="AL242" s="7"/>
       <c r="AM242" s="7"/>
       <c r="AN242" s="7"/>
-    </row>
-    <row r="243" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO242" s="7"/>
+      <c r="AP242" s="7"/>
+      <c r="AQ242" s="7"/>
+      <c r="AR242" s="7"/>
+    </row>
+    <row r="243" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C243" s="7"/>
       <c r="D243" s="7"/>
       <c r="E243" s="7"/>
@@ -11939,8 +13039,12 @@
       <c r="AL243" s="7"/>
       <c r="AM243" s="7"/>
       <c r="AN243" s="7"/>
-    </row>
-    <row r="244" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO243" s="7"/>
+      <c r="AP243" s="7"/>
+      <c r="AQ243" s="7"/>
+      <c r="AR243" s="7"/>
+    </row>
+    <row r="244" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C244" s="7"/>
       <c r="D244" s="7"/>
       <c r="E244" s="7"/>
@@ -11979,8 +13083,12 @@
       <c r="AL244" s="7"/>
       <c r="AM244" s="7"/>
       <c r="AN244" s="7"/>
-    </row>
-    <row r="245" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO244" s="7"/>
+      <c r="AP244" s="7"/>
+      <c r="AQ244" s="7"/>
+      <c r="AR244" s="7"/>
+    </row>
+    <row r="245" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C245" s="7"/>
       <c r="D245" s="7"/>
       <c r="E245" s="7"/>
@@ -12019,8 +13127,12 @@
       <c r="AL245" s="7"/>
       <c r="AM245" s="7"/>
       <c r="AN245" s="7"/>
-    </row>
-    <row r="246" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO245" s="7"/>
+      <c r="AP245" s="7"/>
+      <c r="AQ245" s="7"/>
+      <c r="AR245" s="7"/>
+    </row>
+    <row r="246" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C246" s="7"/>
       <c r="D246" s="7"/>
       <c r="E246" s="7"/>
@@ -12059,8 +13171,12 @@
       <c r="AL246" s="7"/>
       <c r="AM246" s="7"/>
       <c r="AN246" s="7"/>
-    </row>
-    <row r="247" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO246" s="7"/>
+      <c r="AP246" s="7"/>
+      <c r="AQ246" s="7"/>
+      <c r="AR246" s="7"/>
+    </row>
+    <row r="247" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C247" s="7"/>
       <c r="D247" s="7"/>
       <c r="E247" s="7"/>
@@ -12099,8 +13215,12 @@
       <c r="AL247" s="7"/>
       <c r="AM247" s="7"/>
       <c r="AN247" s="7"/>
-    </row>
-    <row r="248" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO247" s="7"/>
+      <c r="AP247" s="7"/>
+      <c r="AQ247" s="7"/>
+      <c r="AR247" s="7"/>
+    </row>
+    <row r="248" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C248" s="7"/>
       <c r="D248" s="7"/>
       <c r="E248" s="7"/>
@@ -12139,8 +13259,12 @@
       <c r="AL248" s="7"/>
       <c r="AM248" s="7"/>
       <c r="AN248" s="7"/>
-    </row>
-    <row r="249" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO248" s="7"/>
+      <c r="AP248" s="7"/>
+      <c r="AQ248" s="7"/>
+      <c r="AR248" s="7"/>
+    </row>
+    <row r="249" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C249" s="7"/>
       <c r="D249" s="7"/>
       <c r="E249" s="7"/>
@@ -12179,8 +13303,12 @@
       <c r="AL249" s="7"/>
       <c r="AM249" s="7"/>
       <c r="AN249" s="7"/>
-    </row>
-    <row r="250" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO249" s="7"/>
+      <c r="AP249" s="7"/>
+      <c r="AQ249" s="7"/>
+      <c r="AR249" s="7"/>
+    </row>
+    <row r="250" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C250" s="7"/>
       <c r="D250" s="7"/>
       <c r="E250" s="7"/>
@@ -12219,8 +13347,12 @@
       <c r="AL250" s="7"/>
       <c r="AM250" s="7"/>
       <c r="AN250" s="7"/>
-    </row>
-    <row r="251" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO250" s="7"/>
+      <c r="AP250" s="7"/>
+      <c r="AQ250" s="7"/>
+      <c r="AR250" s="7"/>
+    </row>
+    <row r="251" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C251" s="7"/>
       <c r="D251" s="7"/>
       <c r="E251" s="7"/>
@@ -12259,8 +13391,12 @@
       <c r="AL251" s="7"/>
       <c r="AM251" s="7"/>
       <c r="AN251" s="7"/>
-    </row>
-    <row r="252" spans="3:40" x14ac:dyDescent="0.2">
+      <c r="AO251" s="7"/>
+      <c r="AP251" s="7"/>
+      <c r="AQ251" s="7"/>
+      <c r="AR251" s="7"/>
+    </row>
+    <row r="252" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C252" s="7"/>
       <c r="D252" s="7"/>
       <c r="E252" s="7"/>
@@ -12299,6 +13435,10 @@
       <c r="AL252" s="7"/>
       <c r="AM252" s="7"/>
       <c r="AN252" s="7"/>
+      <c r="AO252" s="7"/>
+      <c r="AP252" s="7"/>
+      <c r="AQ252" s="7"/>
+      <c r="AR252" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/AS.xlsx
+++ b/AS.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EBEF13-7B35-4B8D-9E88-4D8955824805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{53BA411E-2A41-4FEC-A342-AE8C41391E29}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53BA411E-2A41-4FEC-A342-AE8C41391E29}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
